--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-26.xlsx
@@ -1204,7 +1204,7 @@
     <t>Independiente (Ecu)</t>
   </si>
   <si>
-    <t>2026-07-24 01:46:34</t>
+    <t>2026-07-24 04:03:18</t>
   </si>
 </sst>
 </file>
@@ -1810,13 +1810,13 @@
         <v>7.6</v>
       </c>
       <c r="J2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M2">
         <v>1.04</v>
@@ -1960,25 +1960,25 @@
         <v>4.4</v>
       </c>
       <c r="BH2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO2">
         <v>3.25</v>
@@ -1987,37 +1987,37 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ2">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BR2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BT2">
         <v>11</v>
       </c>
       <c r="BU2">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV2">
         <v>60</v>
       </c>
       <c r="BW2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX2">
         <v>60</v>
       </c>
       <c r="BY2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="CB2" t="s">
         <v>396</v>
@@ -2043,106 +2043,106 @@
         <v>1.26</v>
       </c>
       <c r="G3">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="H3">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="I3">
-        <v>870</v>
+        <v>21</v>
       </c>
       <c r="J3">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="K3">
-        <v>520</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="O3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P3">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="Q3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R3">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S3">
         <v>2.66</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="V3">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W3">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AA3">
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AO3">
         <v>1000</v>
@@ -2196,64 +2196,64 @@
         <v>1.03</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG3">
         <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -2300,7 +2300,7 @@
         <v>3.8</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M4">
         <v>1.1</v>
@@ -2312,16 +2312,16 @@
         <v>1.49</v>
       </c>
       <c r="P4">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q4">
         <v>2.4</v>
       </c>
       <c r="R4">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="T4">
         <v>2.22</v>
@@ -2336,7 +2336,7 @@
         <v>2.2</v>
       </c>
       <c r="X4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y4">
         <v>17</v>
@@ -2393,52 +2393,52 @@
         <v>4.8</v>
       </c>
       <c r="AQ4">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AR4">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS4">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT4">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AU4">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW4">
+        <v>8.6</v>
+      </c>
+      <c r="AX4">
+        <v>4.6</v>
+      </c>
+      <c r="AY4">
+        <v>4.9</v>
+      </c>
+      <c r="AZ4">
+        <v>7</v>
+      </c>
+      <c r="BA4">
+        <v>8.6</v>
+      </c>
+      <c r="BB4">
+        <v>6.2</v>
+      </c>
+      <c r="BC4">
+        <v>6.6</v>
+      </c>
+      <c r="BD4">
         <v>7.8</v>
       </c>
-      <c r="AX4">
-        <v>4.3</v>
-      </c>
-      <c r="AY4">
-        <v>4.7</v>
-      </c>
-      <c r="AZ4">
-        <v>6.4</v>
-      </c>
-      <c r="BA4">
-        <v>7.8</v>
-      </c>
-      <c r="BB4">
-        <v>5.7</v>
-      </c>
-      <c r="BC4">
+      <c r="BE4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF4">
         <v>6</v>
-      </c>
-      <c r="BD4">
-        <v>7.2</v>
-      </c>
-      <c r="BE4">
-        <v>8</v>
-      </c>
-      <c r="BF4">
-        <v>5.6</v>
       </c>
       <c r="BG4">
         <v>9.199999999999999</v>
@@ -2524,22 +2524,22 @@
         <v>282</v>
       </c>
       <c r="F5">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="G5">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="H5">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J5">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K5">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2548,10 +2548,10 @@
         <v>1.17</v>
       </c>
       <c r="N5">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O5">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="P5">
         <v>1.4</v>
@@ -2572,10 +2572,10 @@
         <v>1.55</v>
       </c>
       <c r="V5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W5">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -2590,7 +2590,7 @@
         <v>190</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AC5">
         <v>7.8</v>
@@ -2602,7 +2602,7 @@
         <v>140</v>
       </c>
       <c r="AF5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG5">
         <v>15.5</v>
@@ -2614,10 +2614,10 @@
         <v>190</v>
       </c>
       <c r="AJ5">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL5">
         <v>110</v>
@@ -2626,7 +2626,7 @@
         <v>420</v>
       </c>
       <c r="AN5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO5">
         <v>260</v>
@@ -2641,19 +2641,19 @@
         <v>1.03</v>
       </c>
       <c r="AS5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
         <v>4.5</v>
       </c>
       <c r="AU5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AV5">
         <v>16.5</v>
       </c>
       <c r="AW5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
         <v>9.6</v>
@@ -2665,28 +2665,28 @@
         <v>1.03</v>
       </c>
       <c r="BA5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
         <v>1.03</v>
       </c>
       <c r="BC5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>160</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BI5">
         <v>1.97</v>
@@ -2695,7 +2695,7 @@
         <v>20</v>
       </c>
       <c r="BK5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -2704,13 +2704,13 @@
         <v>3.75</v>
       </c>
       <c r="BN5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO5">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BP5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ5">
         <v>3.35</v>
@@ -2722,10 +2722,10 @@
         <v>3.6</v>
       </c>
       <c r="BT5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU5">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV5">
         <v>1000</v>
@@ -2781,7 +2781,7 @@
         <v>3.9</v>
       </c>
       <c r="K6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L6">
         <v>1.31</v>
@@ -2793,10 +2793,10 @@
         <v>5.1</v>
       </c>
       <c r="O6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q6">
         <v>1.65</v>
@@ -2805,7 +2805,7 @@
         <v>1.57</v>
       </c>
       <c r="S6">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T6">
         <v>1.61</v>
@@ -2835,7 +2835,7 @@
         <v>19</v>
       </c>
       <c r="AC6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD6">
         <v>11</v>
@@ -2850,7 +2850,7 @@
         <v>16</v>
       </c>
       <c r="AH6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI6">
         <v>28</v>
@@ -2925,7 +2925,7 @@
         <v>20</v>
       </c>
       <c r="BG6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -3017,7 +3017,7 @@
         <v>4.8</v>
       </c>
       <c r="I7">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -3044,7 +3044,7 @@
         <v>1.76</v>
       </c>
       <c r="R7">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S7">
         <v>2.96</v>
@@ -3080,10 +3080,10 @@
         <v>9.6</v>
       </c>
       <c r="AD7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE7">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AF7">
         <v>12</v>
@@ -3095,7 +3095,7 @@
         <v>18.5</v>
       </c>
       <c r="AI7">
-        <v>530</v>
+        <v>470</v>
       </c>
       <c r="AJ7">
         <v>18.5</v>
@@ -3158,7 +3158,7 @@
         <v>15.5</v>
       </c>
       <c r="BD7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE7">
         <v>36</v>
@@ -3173,19 +3173,19 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BJ7">
         <v>13</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BN7">
         <v>6</v>
@@ -3197,37 +3197,37 @@
         <v>16</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BR7">
         <v>34</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="BT7">
         <v>11.5</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="BV7">
         <v>50</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="BZ7">
         <v>25</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="CB7" t="s">
         <v>396</v>
@@ -3250,7 +3250,7 @@
         <v>285</v>
       </c>
       <c r="F8">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G8">
         <v>2.12</v>
@@ -3259,7 +3259,7 @@
         <v>3.45</v>
       </c>
       <c r="I8">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -3268,7 +3268,7 @@
         <v>4.3</v>
       </c>
       <c r="L8">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M8">
         <v>1.03</v>
@@ -3286,7 +3286,7 @@
         <v>1.6</v>
       </c>
       <c r="R8">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S8">
         <v>2.54</v>
@@ -3319,7 +3319,7 @@
         <v>14</v>
       </c>
       <c r="AC8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8">
         <v>17</v>
@@ -3328,7 +3328,7 @@
         <v>65</v>
       </c>
       <c r="AF8">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AG8">
         <v>12</v>
@@ -3340,7 +3340,7 @@
         <v>85</v>
       </c>
       <c r="AJ8">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AK8">
         <v>22</v>
@@ -3349,13 +3349,13 @@
         <v>30</v>
       </c>
       <c r="AM8">
-        <v>620</v>
+        <v>590</v>
       </c>
       <c r="AN8">
         <v>11.5</v>
       </c>
       <c r="AO8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP8">
         <v>17.5</v>
@@ -3406,13 +3406,13 @@
         <v>29</v>
       </c>
       <c r="BF8">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG8">
         <v>21</v>
       </c>
       <c r="BH8">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI8">
         <v>3.5</v>
@@ -3421,16 +3421,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK8">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BN8">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO8">
         <v>4.2</v>
@@ -3439,37 +3439,37 @@
         <v>14</v>
       </c>
       <c r="BQ8">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU8">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="CB8" t="s">
         <v>396</v>
@@ -3501,7 +3501,7 @@
         <v>2.5</v>
       </c>
       <c r="I9">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J9">
         <v>3</v>
@@ -3513,91 +3513,91 @@
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N9">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O9">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P9">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="Q9">
         <v>1.9</v>
       </c>
       <c r="R9">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="S9">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V9">
         <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP9">
         <v>1.03</v>
@@ -3648,10 +3648,10 @@
         <v>1.03</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH9">
         <v>4.2</v>
@@ -3734,16 +3734,16 @@
         <v>287</v>
       </c>
       <c r="F10">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="G10">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="H10">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J10">
         <v>3.85</v>
@@ -3767,13 +3767,13 @@
         <v>2.08</v>
       </c>
       <c r="Q10">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="R10">
         <v>1.18</v>
       </c>
       <c r="S10">
-        <v>2.78</v>
+        <v>1.64</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3782,10 +3782,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W10">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3979,7 +3979,7 @@
         <v>2.24</v>
       </c>
       <c r="G11">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H11">
         <v>2.9</v>
@@ -3988,7 +3988,7 @@
         <v>3.35</v>
       </c>
       <c r="J11">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K11">
         <v>4.2</v>
@@ -4006,10 +4006,10 @@
         <v>1.25</v>
       </c>
       <c r="P11">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q11">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R11">
         <v>1.38</v>
@@ -4221,16 +4221,16 @@
         <v>2.16</v>
       </c>
       <c r="G12">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H12">
         <v>4.1</v>
       </c>
       <c r="I12">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J12">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K12">
         <v>3.35</v>
@@ -4242,19 +4242,19 @@
         <v>1.1</v>
       </c>
       <c r="N12">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O12">
         <v>1.41</v>
       </c>
       <c r="P12">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q12">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R12">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S12">
         <v>4.1</v>
@@ -4263,7 +4263,7 @@
         <v>1.9</v>
       </c>
       <c r="U12">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V12">
         <v>1.28</v>
@@ -4299,7 +4299,7 @@
         <v>13.5</v>
       </c>
       <c r="AG12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH12">
         <v>18.5</v>
@@ -4308,10 +4308,10 @@
         <v>90</v>
       </c>
       <c r="AJ12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK12">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL12">
         <v>48</v>
@@ -4326,7 +4326,7 @@
         <v>90</v>
       </c>
       <c r="AP12">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ12">
         <v>10</v>
@@ -4335,7 +4335,7 @@
         <v>21</v>
       </c>
       <c r="AS12">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT12">
         <v>7.6</v>
@@ -4347,7 +4347,7 @@
         <v>14.5</v>
       </c>
       <c r="AW12">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX12">
         <v>9.800000000000001</v>
@@ -4359,10 +4359,10 @@
         <v>15.5</v>
       </c>
       <c r="BA12">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB12">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC12">
         <v>21</v>
@@ -4371,13 +4371,13 @@
         <v>34</v>
       </c>
       <c r="BE12">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF12">
         <v>19</v>
       </c>
       <c r="BG12">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -4484,7 +4484,7 @@
         <v>1.03</v>
       </c>
       <c r="N13">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O13">
         <v>1.15</v>
@@ -4493,7 +4493,7 @@
         <v>3.05</v>
       </c>
       <c r="Q13">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R13">
         <v>1.82</v>
@@ -4508,10 +4508,10 @@
         <v>2.94</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W13">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X13">
         <v>34</v>
@@ -4553,7 +4553,7 @@
         <v>30</v>
       </c>
       <c r="AK13">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL13">
         <v>25</v>
@@ -4565,10 +4565,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AP13">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AQ13">
         <v>20</v>
@@ -4589,7 +4589,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX13">
         <v>16.5</v>
@@ -4598,10 +4598,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA13">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BB13">
         <v>19.5</v>
@@ -4622,7 +4622,7 @@
         <v>14.5</v>
       </c>
       <c r="BH13">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BI13">
         <v>4</v>
@@ -4631,13 +4631,13 @@
         <v>8.6</v>
       </c>
       <c r="BK13">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BL13">
         <v>65</v>
       </c>
       <c r="BM13">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BN13">
         <v>6.2</v>
@@ -4649,37 +4649,37 @@
         <v>14.5</v>
       </c>
       <c r="BQ13">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BR13">
         <v>21</v>
       </c>
       <c r="BS13">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT13">
         <v>7.4</v>
       </c>
       <c r="BU13">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW13">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX13">
         <v>25</v>
       </c>
       <c r="BY13">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ13">
         <v>13</v>
       </c>
       <c r="CA13">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="CB13" t="s">
         <v>396</v>
@@ -4702,22 +4702,22 @@
         <v>291</v>
       </c>
       <c r="F14">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G14">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H14">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="I14">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J14">
         <v>3.5</v>
       </c>
       <c r="K14">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4726,19 +4726,19 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="O14">
         <v>1.31</v>
       </c>
       <c r="P14">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q14">
         <v>1.89</v>
       </c>
       <c r="R14">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S14">
         <v>3.2</v>
@@ -4750,10 +4750,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W14">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -5189,22 +5189,22 @@
         <v>1.26</v>
       </c>
       <c r="G16">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="H16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="I16">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J16">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="L16">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M16">
         <v>1.02</v>
@@ -5216,28 +5216,28 @@
         <v>1.11</v>
       </c>
       <c r="P16">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q16">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R16">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S16">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="T16">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U16">
         <v>2.2</v>
       </c>
       <c r="V16">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W16">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="X16">
         <v>55</v>
@@ -5258,7 +5258,7 @@
         <v>20</v>
       </c>
       <c r="AD16">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AE16">
         <v>1000</v>
@@ -5270,7 +5270,7 @@
         <v>12</v>
       </c>
       <c r="AH16">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI16">
         <v>110</v>
@@ -5312,7 +5312,7 @@
         <v>16</v>
       </c>
       <c r="AV16">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AW16">
         <v>44</v>
@@ -5342,7 +5342,7 @@
         <v>38</v>
       </c>
       <c r="BF16">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BG16">
         <v>42</v>
@@ -5351,55 +5351,55 @@
         <v>5.9</v>
       </c>
       <c r="BI16">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BJ16">
         <v>11</v>
       </c>
       <c r="BK16">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN16">
         <v>4.4</v>
       </c>
       <c r="BO16">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP16">
         <v>7</v>
       </c>
       <c r="BQ16">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BS16">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BU16">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
+        <v>13.5</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
         <v>12.5</v>
-      </c>
-      <c r="BX16">
-        <v>60</v>
-      </c>
-      <c r="BY16">
-        <v>12</v>
       </c>
       <c r="BZ16">
         <v>7.2</v>
@@ -5428,16 +5428,16 @@
         <v>294</v>
       </c>
       <c r="F17">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G17">
         <v>2.6</v>
       </c>
       <c r="H17">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I17">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -5446,37 +5446,37 @@
         <v>4.3</v>
       </c>
       <c r="L17">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M17">
         <v>1.03</v>
       </c>
       <c r="N17">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O17">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P17">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q17">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R17">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S17">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T17">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U17">
         <v>2.88</v>
       </c>
       <c r="V17">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W17">
         <v>1.63</v>
@@ -5485,7 +5485,7 @@
         <v>55</v>
       </c>
       <c r="Y17">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Z17">
         <v>34</v>
@@ -5581,7 +5581,7 @@
         <v>18</v>
       </c>
       <c r="BE17">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BF17">
         <v>10.5</v>
@@ -5590,25 +5590,25 @@
         <v>11.5</v>
       </c>
       <c r="BH17">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BI17">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BJ17">
         <v>8.4</v>
       </c>
       <c r="BK17">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN17">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO17">
         <v>4.9</v>
@@ -5617,13 +5617,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ17">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT17">
         <v>6.6</v>
@@ -5635,19 +5635,19 @@
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ17">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CA17">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="CB17" t="s">
         <v>396</v>
@@ -5670,58 +5670,58 @@
         <v>295</v>
       </c>
       <c r="F18">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G18">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="H18">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J18">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K18">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L18">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="M18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N18">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O18">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P18">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q18">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R18">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S18">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="T18">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U18">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="V18">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="X18">
         <v>36</v>
@@ -5730,7 +5730,7 @@
         <v>26</v>
       </c>
       <c r="Z18">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA18">
         <v>1000</v>
@@ -5742,13 +5742,13 @@
         <v>12</v>
       </c>
       <c r="AD18">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AE18">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF18">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AG18">
         <v>11.5</v>
@@ -5760,22 +5760,22 @@
         <v>70</v>
       </c>
       <c r="AJ18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK18">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL18">
         <v>25</v>
       </c>
       <c r="AM18">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN18">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AO18">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP18">
         <v>21</v>
@@ -5784,22 +5784,22 @@
         <v>21</v>
       </c>
       <c r="AR18">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS18">
         <v>34</v>
       </c>
       <c r="AT18">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AU18">
         <v>10</v>
       </c>
       <c r="AV18">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW18">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX18">
         <v>14</v>
@@ -5808,7 +5808,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA18">
         <v>22</v>
@@ -5826,10 +5826,10 @@
         <v>27</v>
       </c>
       <c r="BF18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG18">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BH18">
         <v>5.2</v>
@@ -5838,49 +5838,49 @@
         <v>4</v>
       </c>
       <c r="BJ18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK18">
+        <v>4.7</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
         <v>9</v>
       </c>
-      <c r="BK18">
-        <v>4.8</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BN18">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO18">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP18">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ18">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="BR18">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BS18">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT18">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU18">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BV18">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BW18">
         <v>7.4</v>
       </c>
       <c r="BX18">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
         <v>7.6</v>
@@ -5889,7 +5889,7 @@
         <v>12.5</v>
       </c>
       <c r="CA18">
-        <v>9.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="CB18" t="s">
         <v>396</v>
@@ -5915,22 +5915,22 @@
         <v>1.94</v>
       </c>
       <c r="G19">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H19">
         <v>3.9</v>
       </c>
       <c r="I19">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J19">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K19">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M19">
         <v>1.06</v>
@@ -5948,7 +5948,7 @@
         <v>1.87</v>
       </c>
       <c r="R19">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S19">
         <v>3.2</v>
@@ -5963,7 +5963,7 @@
         <v>1.29</v>
       </c>
       <c r="W19">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="X19">
         <v>18</v>
@@ -5978,7 +5978,7 @@
         <v>100</v>
       </c>
       <c r="AB19">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC19">
         <v>9.800000000000001</v>
@@ -5993,7 +5993,7 @@
         <v>14.5</v>
       </c>
       <c r="AG19">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH19">
         <v>21</v>
@@ -6020,10 +6020,10 @@
         <v>60</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR19">
         <v>1.03</v>
@@ -6032,13 +6032,13 @@
         <v>1.03</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW19">
         <v>1.03</v>
@@ -6047,19 +6047,19 @@
         <v>1.03</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA19">
         <v>1.03</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD19">
         <v>1.03</v>
@@ -6411,7 +6411,7 @@
         <v>5.1</v>
       </c>
       <c r="K21">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -6438,7 +6438,7 @@
         <v>2.56</v>
       </c>
       <c r="T21">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="U21">
         <v>2</v>
@@ -6462,7 +6462,7 @@
         <v>250</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC21">
         <v>13</v>
@@ -6510,10 +6510,10 @@
         <v>21</v>
       </c>
       <c r="AR21">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AS21">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT21">
         <v>8.800000000000001</v>
@@ -6525,7 +6525,7 @@
         <v>19</v>
       </c>
       <c r="AW21">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AX21">
         <v>8.6</v>
@@ -6537,7 +6537,7 @@
         <v>20</v>
       </c>
       <c r="BA21">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB21">
         <v>11</v>
@@ -6549,19 +6549,19 @@
         <v>24</v>
       </c>
       <c r="BE21">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF21">
         <v>5.2</v>
       </c>
       <c r="BG21">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH21">
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BJ21">
         <v>15</v>
@@ -6573,7 +6573,7 @@
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BN21">
         <v>5.4</v>
@@ -6585,16 +6585,16 @@
         <v>11.5</v>
       </c>
       <c r="BQ21">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BR21">
         <v>30</v>
       </c>
       <c r="BS21">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BT21">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BU21">
         <v>1.82</v>
@@ -6603,13 +6603,13 @@
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BZ21">
         <v>18</v>
@@ -6910,7 +6910,7 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q23">
         <v>1.01</v>
@@ -7606,154 +7606,154 @@
         <v>303</v>
       </c>
       <c r="F26">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="G26">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="H26">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="I26">
+        <v>6.4</v>
+      </c>
+      <c r="J26">
+        <v>3.75</v>
+      </c>
+      <c r="K26">
+        <v>4.4</v>
+      </c>
+      <c r="L26">
+        <v>1.01</v>
+      </c>
+      <c r="M26">
+        <v>1.06</v>
+      </c>
+      <c r="N26">
+        <v>3.65</v>
+      </c>
+      <c r="O26">
+        <v>1.3</v>
+      </c>
+      <c r="P26">
+        <v>1.93</v>
+      </c>
+      <c r="Q26">
+        <v>1.88</v>
+      </c>
+      <c r="R26">
+        <v>1.35</v>
+      </c>
+      <c r="S26">
+        <v>3.25</v>
+      </c>
+      <c r="T26">
+        <v>1.86</v>
+      </c>
+      <c r="U26">
+        <v>1.95</v>
+      </c>
+      <c r="V26">
+        <v>1.18</v>
+      </c>
+      <c r="W26">
+        <v>2.24</v>
+      </c>
+      <c r="X26">
+        <v>16</v>
+      </c>
+      <c r="Y26">
+        <v>20</v>
+      </c>
+      <c r="Z26">
+        <v>55</v>
+      </c>
+      <c r="AA26">
+        <v>180</v>
+      </c>
+      <c r="AB26">
         <v>8.800000000000001</v>
       </c>
-      <c r="J26">
-        <v>3.25</v>
-      </c>
-      <c r="K26">
-        <v>8.4</v>
-      </c>
-      <c r="L26">
-        <v>1.01</v>
-      </c>
-      <c r="M26">
-        <v>1.01</v>
-      </c>
-      <c r="N26">
-        <v>1.75</v>
-      </c>
-      <c r="O26">
-        <v>1.27</v>
-      </c>
-      <c r="P26">
-        <v>1.75</v>
-      </c>
-      <c r="Q26">
-        <v>1.74</v>
-      </c>
-      <c r="R26">
-        <v>1.18</v>
-      </c>
-      <c r="S26">
-        <v>1.74</v>
-      </c>
-      <c r="T26">
-        <v>1.01</v>
-      </c>
-      <c r="U26">
-        <v>1.01</v>
-      </c>
-      <c r="V26">
-        <v>1.13</v>
-      </c>
-      <c r="W26">
-        <v>2.02</v>
-      </c>
-      <c r="X26">
-        <v>1000</v>
-      </c>
-      <c r="Y26">
-        <v>1000</v>
-      </c>
-      <c r="Z26">
-        <v>1000</v>
-      </c>
-      <c r="AA26">
-        <v>1000</v>
-      </c>
-      <c r="AB26">
-        <v>1000</v>
-      </c>
       <c r="AC26">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF26">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG26">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH26">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP26">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ26">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AR26">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="AS26">
         <v>1.03</v>
       </c>
       <c r="AT26">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU26">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV26">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AW26">
         <v>1.03</v>
       </c>
       <c r="AX26">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AY26">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ26">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA26">
         <v>1.03</v>
       </c>
       <c r="BB26">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BC26">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BD26">
         <v>1.03</v>
@@ -7762,10 +7762,10 @@
         <v>1.03</v>
       </c>
       <c r="BF26">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG26">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7848,7 +7848,7 @@
         <v>304</v>
       </c>
       <c r="F27">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G27">
         <v>1.95</v>
@@ -7857,7 +7857,7 @@
         <v>4.5</v>
       </c>
       <c r="I27">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="J27">
         <v>3.65</v>
@@ -9306,7 +9306,7 @@
         <v>2.08</v>
       </c>
       <c r="H33">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I33">
         <v>7.8</v>
@@ -9545,10 +9545,10 @@
         <v>1.79</v>
       </c>
       <c r="G34">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H34">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I34">
         <v>4.7</v>
@@ -9787,10 +9787,10 @@
         <v>3.65</v>
       </c>
       <c r="G35">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I35">
         <v>2.16</v>
@@ -9814,7 +9814,7 @@
         <v>1.25</v>
       </c>
       <c r="P35">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -9829,7 +9829,7 @@
         <v>1.65</v>
       </c>
       <c r="U35">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V35">
         <v>1.86</v>
@@ -9946,22 +9946,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BH35">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI35">
         <v>3.15</v>
       </c>
       <c r="BJ35">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK35">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>12.5</v>
+        <v>3</v>
       </c>
       <c r="BN35">
         <v>7.2</v>
@@ -9973,16 +9973,16 @@
         <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT35">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU35">
         <v>4.1</v>
@@ -9991,13 +9991,13 @@
         <v>14.5</v>
       </c>
       <c r="BW35">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ35">
         <v>0</v>
@@ -10059,13 +10059,13 @@
         <v>1.83</v>
       </c>
       <c r="Q36">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="R36">
         <v>1.18</v>
       </c>
       <c r="S36">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="T36">
         <v>1.01</v>
@@ -10298,7 +10298,7 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q37">
         <v>1.01</v>
@@ -10752,10 +10752,10 @@
         <v>316</v>
       </c>
       <c r="F39">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="G39">
-        <v>600</v>
+        <v>2.22</v>
       </c>
       <c r="H39">
         <v>3.2</v>
@@ -10764,10 +10764,10 @@
         <v>3.55</v>
       </c>
       <c r="J39">
-        <v>1.39</v>
+        <v>4.1</v>
       </c>
       <c r="K39">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10782,7 +10782,7 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="Q39">
         <v>1.46</v>
@@ -11024,7 +11024,7 @@
         <v>0</v>
       </c>
       <c r="P40">
-        <v>2.42</v>
+        <v>1.25</v>
       </c>
       <c r="Q40">
         <v>1.43</v>
@@ -11236,10 +11236,10 @@
         <v>318</v>
       </c>
       <c r="F41">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H41">
         <v>3.7</v>
@@ -11478,7 +11478,7 @@
         <v>319</v>
       </c>
       <c r="F42">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="G42">
         <v>7.6</v>
@@ -11490,7 +11490,7 @@
         <v>1.51</v>
       </c>
       <c r="J42">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K42">
         <v>5.5</v>
@@ -11720,22 +11720,22 @@
         <v>320</v>
       </c>
       <c r="F43">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G43">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H43">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I43">
         <v>7.2</v>
       </c>
       <c r="J43">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K43">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -11750,10 +11750,10 @@
         <v>0</v>
       </c>
       <c r="P43">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Q43">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -12234,7 +12234,7 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q45">
         <v>1.8</v>
@@ -12446,16 +12446,16 @@
         <v>323</v>
       </c>
       <c r="F46">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G46">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H46">
         <v>1.62</v>
       </c>
       <c r="I46">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="J46">
         <v>4.6</v>
@@ -12700,7 +12700,7 @@
         <v>2.9</v>
       </c>
       <c r="J47">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K47">
         <v>3.75</v>
@@ -12718,10 +12718,10 @@
         <v>0</v>
       </c>
       <c r="P47">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="Q47">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="R47">
         <v>0</v>
@@ -12936,13 +12936,13 @@
         <v>2.04</v>
       </c>
       <c r="H48">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I48">
+        <v>4</v>
+      </c>
+      <c r="J48">
         <v>4.1</v>
-      </c>
-      <c r="J48">
-        <v>4.2</v>
       </c>
       <c r="K48">
         <v>4.7</v>
@@ -12960,7 +12960,7 @@
         <v>0</v>
       </c>
       <c r="P48">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q48">
         <v>1.47</v>
@@ -13656,22 +13656,22 @@
         <v>328</v>
       </c>
       <c r="F51">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="G51">
-        <v>2.64</v>
+        <v>2.38</v>
       </c>
       <c r="H51">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I51">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J51">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="K51">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -13686,10 +13686,10 @@
         <v>0</v>
       </c>
       <c r="P51">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="Q51">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="R51">
         <v>0</v>
@@ -13916,7 +13916,7 @@
         <v>4.6</v>
       </c>
       <c r="L52">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M52">
         <v>1.07</v>
@@ -13955,7 +13955,7 @@
         <v>17.5</v>
       </c>
       <c r="Y52">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z52">
         <v>60</v>
@@ -13964,10 +13964,10 @@
         <v>240</v>
       </c>
       <c r="AB52">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC52">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD52">
         <v>27</v>
@@ -13976,7 +13976,7 @@
         <v>130</v>
       </c>
       <c r="AF52">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG52">
         <v>12</v>
@@ -13991,10 +13991,10 @@
         <v>16</v>
       </c>
       <c r="AK52">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL52">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM52">
         <v>170</v>
@@ -14012,34 +14012,34 @@
         <v>17.5</v>
       </c>
       <c r="AR52">
+        <v>5.4</v>
+      </c>
+      <c r="AS52">
+        <v>5.8</v>
+      </c>
+      <c r="AT52">
+        <v>6.6</v>
+      </c>
+      <c r="AU52">
+        <v>3.85</v>
+      </c>
+      <c r="AV52">
         <v>4.9</v>
       </c>
-      <c r="AS52">
-        <v>5.3</v>
-      </c>
-      <c r="AT52">
-        <v>3.4</v>
-      </c>
-      <c r="AU52">
-        <v>3.65</v>
-      </c>
-      <c r="AV52">
-        <v>4.5</v>
-      </c>
       <c r="AW52">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX52">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY52">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="AZ52">
         <v>20</v>
       </c>
       <c r="BA52">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB52">
         <v>12.5</v>
@@ -14048,16 +14048,16 @@
         <v>15</v>
       </c>
       <c r="BD52">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BE52">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF52">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BG52">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH52">
         <v>3.6</v>
@@ -14069,13 +14069,13 @@
         <v>11.5</v>
       </c>
       <c r="BK52">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL52">
         <v>1000</v>
       </c>
       <c r="BM52">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN52">
         <v>4.2</v>
@@ -14087,31 +14087,31 @@
         <v>11</v>
       </c>
       <c r="BQ52">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR52">
         <v>29</v>
       </c>
       <c r="BS52">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT52">
         <v>10.5</v>
       </c>
       <c r="BU52">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV52">
         <v>1000</v>
       </c>
       <c r="BW52">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX52">
         <v>1000</v>
       </c>
       <c r="BY52">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ52">
         <v>0</v>
@@ -14140,13 +14140,13 @@
         <v>330</v>
       </c>
       <c r="F53">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="G53">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="H53">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="I53">
         <v>28</v>
@@ -14155,7 +14155,7 @@
         <v>7.4</v>
       </c>
       <c r="K53">
-        <v>950</v>
+        <v>8.6</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>2.72</v>
       </c>
       <c r="Q53">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R53">
         <v>0</v>
@@ -14412,10 +14412,10 @@
         <v>0</v>
       </c>
       <c r="P54">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q54">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -14624,22 +14624,22 @@
         <v>332</v>
       </c>
       <c r="F55">
-        <v>2.18</v>
+        <v>4.5</v>
       </c>
       <c r="G55">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H55">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I55">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J55">
         <v>3.95</v>
       </c>
       <c r="K55">
-        <v>500</v>
+        <v>5.3</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -14654,10 +14654,10 @@
         <v>0</v>
       </c>
       <c r="P55">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q55">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -15595,13 +15595,13 @@
         <v>1.43</v>
       </c>
       <c r="G59">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H59">
         <v>7.6</v>
       </c>
       <c r="I59">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J59">
         <v>5.3</v>
@@ -16076,22 +16076,22 @@
         <v>338</v>
       </c>
       <c r="F61">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="G61">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="H61">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I61">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J61">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="K61">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -16106,10 +16106,10 @@
         <v>0</v>
       </c>
       <c r="P61">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q61">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="R61">
         <v>0</v>
@@ -16318,22 +16318,22 @@
         <v>339</v>
       </c>
       <c r="F62">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="G62">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H62">
         <v>2.48</v>
       </c>
       <c r="I62">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="J62">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K62">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>0</v>
       </c>
       <c r="P62">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="Q62">
         <v>2.08</v>
@@ -16560,16 +16560,16 @@
         <v>340</v>
       </c>
       <c r="F63">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="G63">
         <v>2.02</v>
       </c>
       <c r="H63">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I63">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J63">
         <v>4</v>
@@ -16590,7 +16590,7 @@
         <v>0</v>
       </c>
       <c r="P63">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q63">
         <v>1.68</v>
@@ -16805,7 +16805,7 @@
         <v>1.37</v>
       </c>
       <c r="G64">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="H64">
         <v>8.800000000000001</v>
@@ -16814,7 +16814,7 @@
         <v>10.5</v>
       </c>
       <c r="J64">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K64">
         <v>5.8</v>
@@ -16835,7 +16835,7 @@
         <v>2.38</v>
       </c>
       <c r="Q64">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R64">
         <v>0</v>
@@ -17056,7 +17056,7 @@
         <v>7</v>
       </c>
       <c r="J65">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K65">
         <v>5.4</v>
@@ -17286,13 +17286,13 @@
         <v>343</v>
       </c>
       <c r="F66">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G66">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H66">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I66">
         <v>5</v>
@@ -17528,76 +17528,76 @@
         <v>344</v>
       </c>
       <c r="F67">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="G67">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H67">
         <v>2.34</v>
       </c>
       <c r="I67">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="J67">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K67">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L67">
         <v>1.01</v>
       </c>
       <c r="M67">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N67">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="O67">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P67">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q67">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="R67">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S67">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="T67">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U67">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V67">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W67">
         <v>1.44</v>
       </c>
       <c r="X67">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y67">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z67">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA67">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB67">
         <v>16.5</v>
       </c>
       <c r="AC67">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD67">
         <v>14</v>
@@ -17606,10 +17606,10 @@
         <v>32</v>
       </c>
       <c r="AF67">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG67">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH67">
         <v>20</v>
@@ -17621,46 +17621,46 @@
         <v>65</v>
       </c>
       <c r="AK67">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL67">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM67">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN67">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO67">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP67">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ67">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AR67">
         <v>12</v>
       </c>
       <c r="AS67">
-        <v>24</v>
+        <v>3.85</v>
       </c>
       <c r="AT67">
         <v>10</v>
       </c>
       <c r="AU67">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV67">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AW67">
         <v>18</v>
       </c>
       <c r="AX67">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY67">
         <v>10</v>
@@ -17669,43 +17669,43 @@
         <v>12</v>
       </c>
       <c r="BA67">
-        <v>25</v>
+        <v>3.9</v>
       </c>
       <c r="BB67">
+        <v>4</v>
+      </c>
+      <c r="BC67">
         <v>3.9</v>
       </c>
-      <c r="BC67">
-        <v>3.8</v>
-      </c>
       <c r="BD67">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BE67">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF67">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG67">
         <v>13</v>
       </c>
       <c r="BH67">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BI67">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BJ67">
         <v>9.199999999999999</v>
       </c>
       <c r="BK67">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BL67">
         <v>1000</v>
       </c>
       <c r="BM67">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BN67">
         <v>6.4</v>
@@ -17717,31 +17717,31 @@
         <v>1000</v>
       </c>
       <c r="BQ67">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR67">
         <v>1000</v>
       </c>
       <c r="BS67">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT67">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BU67">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV67">
         <v>1000</v>
       </c>
       <c r="BW67">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BX67">
         <v>1000</v>
       </c>
       <c r="BY67">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ67">
         <v>0</v>
@@ -17770,7 +17770,7 @@
         <v>345</v>
       </c>
       <c r="F68">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="G68">
         <v>1.95</v>
@@ -17782,7 +17782,7 @@
         <v>870</v>
       </c>
       <c r="J68">
-        <v>2.04</v>
+        <v>4.2</v>
       </c>
       <c r="K68">
         <v>500</v>
@@ -17800,10 +17800,10 @@
         <v>0</v>
       </c>
       <c r="P68">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="Q68">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="R68">
         <v>0</v>
@@ -18012,22 +18012,22 @@
         <v>346</v>
       </c>
       <c r="F69">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="G69">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="H69">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="I69">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="J69">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K69">
-        <v>500</v>
+        <v>4.1</v>
       </c>
       <c r="L69">
         <v>0</v>
@@ -18042,10 +18042,10 @@
         <v>0</v>
       </c>
       <c r="P69">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="Q69">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -18260,7 +18260,7 @@
         <v>1.87</v>
       </c>
       <c r="H70">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I70">
         <v>4.8</v>
@@ -18287,7 +18287,7 @@
         <v>2.44</v>
       </c>
       <c r="Q70">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -18544,7 +18544,7 @@
         <v>1.11</v>
       </c>
       <c r="V71">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W71">
         <v>2.18</v>
@@ -18980,7 +18980,7 @@
         <v>350</v>
       </c>
       <c r="F73">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G73">
         <v>4.6</v>
@@ -18989,13 +18989,13 @@
         <v>1.86</v>
       </c>
       <c r="I73">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="J73">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="K73">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -19509,7 +19509,7 @@
         <v>1.35</v>
       </c>
       <c r="U75">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="V75">
         <v>1.45</v>
@@ -19957,7 +19957,7 @@
         <v>2.02</v>
       </c>
       <c r="I77">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J77">
         <v>4</v>
@@ -19966,22 +19966,22 @@
         <v>5.1</v>
       </c>
       <c r="L77">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M77">
         <v>1.02</v>
       </c>
       <c r="N77">
-        <v>2.82</v>
+        <v>6.2</v>
       </c>
       <c r="O77">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P77">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="Q77">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R77">
         <v>1.72</v>
@@ -19990,13 +19990,13 @@
         <v>2.06</v>
       </c>
       <c r="T77">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="U77">
-        <v>2.46</v>
+        <v>1.11</v>
       </c>
       <c r="V77">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W77">
         <v>1.38</v>
@@ -20110,64 +20110,64 @@
         <v>1.01</v>
       </c>
       <c r="BH77">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI77">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BJ77">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK77">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL77">
         <v>1000</v>
       </c>
       <c r="BM77">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BN77">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO77">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BP77">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ77">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BR77">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS77">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BT77">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU77">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV77">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW77">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX77">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY77">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BZ77">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA77">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB77" t="s">
         <v>396</v>
@@ -20193,10 +20193,10 @@
         <v>7.2</v>
       </c>
       <c r="G78">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="H78">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I78">
         <v>1.47</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="P78">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q78">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -20441,7 +20441,7 @@
         <v>2.98</v>
       </c>
       <c r="I79">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J79">
         <v>3.4</v>
@@ -20674,7 +20674,7 @@
         <v>357</v>
       </c>
       <c r="F80">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G80">
         <v>1.8</v>
@@ -20704,10 +20704,10 @@
         <v>0</v>
       </c>
       <c r="P80">
-        <v>1.07</v>
+        <v>1.96</v>
       </c>
       <c r="Q80">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -21161,7 +21161,7 @@
         <v>1.75</v>
       </c>
       <c r="G82">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H82">
         <v>5.4</v>
@@ -21170,10 +21170,10 @@
         <v>7</v>
       </c>
       <c r="J82">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K82">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -21188,10 +21188,10 @@
         <v>0</v>
       </c>
       <c r="P82">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q82">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -21200,10 +21200,10 @@
         <v>0</v>
       </c>
       <c r="T82">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U82">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V82">
         <v>0</v>
@@ -21260,10 +21260,10 @@
         <v>210</v>
       </c>
       <c r="AN82">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO82">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP82">
         <v>8.199999999999999</v>
@@ -21272,13 +21272,13 @@
         <v>11.5</v>
       </c>
       <c r="AR82">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS82">
         <v>4.3</v>
       </c>
       <c r="AT82">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="AU82">
         <v>6.2</v>
@@ -21290,16 +21290,16 @@
         <v>4.2</v>
       </c>
       <c r="AX82">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AY82">
         <v>7.6</v>
       </c>
       <c r="AZ82">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA82">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB82">
         <v>14</v>
@@ -21406,7 +21406,7 @@
         <v>4.2</v>
       </c>
       <c r="H83">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I83">
         <v>1.99</v>
@@ -21430,7 +21430,7 @@
         <v>0</v>
       </c>
       <c r="P83">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q83">
         <v>1.69</v>
@@ -21642,145 +21642,145 @@
         <v>361</v>
       </c>
       <c r="F84">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G84">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="H84">
         <v>3.1</v>
       </c>
       <c r="I84">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J84">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K84">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="L84">
         <v>1.01</v>
       </c>
       <c r="M84">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N84">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="O84">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P84">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q84">
+        <v>1.65</v>
+      </c>
+      <c r="R84">
+        <v>1.45</v>
+      </c>
+      <c r="S84">
+        <v>2.86</v>
+      </c>
+      <c r="T84">
+        <v>1.56</v>
+      </c>
+      <c r="U84">
+        <v>2.14</v>
+      </c>
+      <c r="V84">
+        <v>1.4</v>
+      </c>
+      <c r="W84">
         <v>1.71</v>
       </c>
-      <c r="R84">
-        <v>1.39</v>
-      </c>
-      <c r="S84">
-        <v>1.05</v>
-      </c>
-      <c r="T84">
-        <v>1.11</v>
-      </c>
-      <c r="U84">
-        <v>1.11</v>
-      </c>
-      <c r="V84">
-        <v>1.34</v>
-      </c>
-      <c r="W84">
-        <v>1.64</v>
-      </c>
       <c r="X84">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y84">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z84">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA84">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB84">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC84">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD84">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE84">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF84">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG84">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH84">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI84">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ84">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK84">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL84">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM84">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN84">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO84">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP84">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ84">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR84">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AS84">
         <v>1.03</v>
       </c>
       <c r="AT84">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU84">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV84">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW84">
         <v>1.03</v>
       </c>
       <c r="AX84">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY84">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ84">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA84">
         <v>1.03</v>
@@ -21789,7 +21789,7 @@
         <v>1.03</v>
       </c>
       <c r="BC84">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BD84">
         <v>1.03</v>
@@ -21798,10 +21798,10 @@
         <v>1.03</v>
       </c>
       <c r="BF84">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG84">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH84">
         <v>1000</v>
@@ -22368,16 +22368,16 @@
         <v>364</v>
       </c>
       <c r="F87">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="G87">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="H87">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="I87">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="J87">
         <v>4.8</v>
@@ -22413,28 +22413,28 @@
         <v>1.57</v>
       </c>
       <c r="U87">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V87">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="W87">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X87">
         <v>36</v>
       </c>
       <c r="Y87">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z87">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA87">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AB87">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AC87">
         <v>13.5</v>
@@ -22443,40 +22443,40 @@
         <v>11.5</v>
       </c>
       <c r="AE87">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AF87">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AG87">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AH87">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI87">
         <v>25</v>
       </c>
       <c r="AJ87">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AK87">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AL87">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AM87">
         <v>65</v>
       </c>
       <c r="AN87">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AO87">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AP87">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ87">
         <v>13</v>
@@ -22488,7 +22488,7 @@
         <v>13.5</v>
       </c>
       <c r="AT87">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU87">
         <v>11</v>
@@ -22500,7 +22500,7 @@
         <v>12</v>
       </c>
       <c r="AX87">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY87">
         <v>20</v>
@@ -22512,19 +22512,19 @@
         <v>20</v>
       </c>
       <c r="BB87">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC87">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD87">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BE87">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BF87">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="BG87">
         <v>4.4</v>
@@ -22545,28 +22545,28 @@
         <v>1000</v>
       </c>
       <c r="BM87">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN87">
         <v>10.5</v>
       </c>
       <c r="BO87">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP87">
+        <v>42</v>
+      </c>
+      <c r="BQ87">
+        <v>8</v>
+      </c>
+      <c r="BR87">
         <v>40</v>
-      </c>
-      <c r="BQ87">
-        <v>7.8</v>
-      </c>
-      <c r="BR87">
-        <v>38</v>
       </c>
       <c r="BS87">
         <v>7.8</v>
       </c>
       <c r="BT87">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU87">
         <v>3.8</v>
@@ -22587,7 +22587,7 @@
         <v>11</v>
       </c>
       <c r="CA87">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="CB87" t="s">
         <v>396</v>
@@ -22613,7 +22613,7 @@
         <v>5.1</v>
       </c>
       <c r="G88">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H88">
         <v>1.68</v>
@@ -22640,10 +22640,10 @@
         <v>0</v>
       </c>
       <c r="P88">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q88">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -22864,7 +22864,7 @@
         <v>3.7</v>
       </c>
       <c r="J89">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="K89">
         <v>5.2</v>
@@ -23578,22 +23578,22 @@
         <v>369</v>
       </c>
       <c r="F92">
-        <v>1.43</v>
+        <v>2.64</v>
       </c>
       <c r="G92">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="H92">
-        <v>2.44</v>
+        <v>2.82</v>
       </c>
       <c r="I92">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J92">
-        <v>1.42</v>
+        <v>3.05</v>
       </c>
       <c r="K92">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -23611,7 +23611,7 @@
         <v>1.25</v>
       </c>
       <c r="Q92">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -23820,22 +23820,22 @@
         <v>370</v>
       </c>
       <c r="F93">
-        <v>2.58</v>
+        <v>5.3</v>
       </c>
       <c r="G93">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="H93">
         <v>1.45</v>
       </c>
       <c r="I93">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="J93">
-        <v>2.58</v>
+        <v>3.55</v>
       </c>
       <c r="K93">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="L93">
         <v>0</v>
@@ -23850,7 +23850,7 @@
         <v>0</v>
       </c>
       <c r="P93">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q93">
         <v>2.08</v>
@@ -24062,22 +24062,22 @@
         <v>371</v>
       </c>
       <c r="F94">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G94">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="H94">
-        <v>2.48</v>
+        <v>5.4</v>
       </c>
       <c r="I94">
-        <v>870</v>
+        <v>7.2</v>
       </c>
       <c r="J94">
-        <v>2.46</v>
+        <v>4.6</v>
       </c>
       <c r="K94">
-        <v>500</v>
+        <v>5.3</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="P94">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="Q94">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -24304,22 +24304,22 @@
         <v>372</v>
       </c>
       <c r="F95">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G95">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H95">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I95">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J95">
         <v>3.4</v>
       </c>
       <c r="K95">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -24334,10 +24334,10 @@
         <v>0</v>
       </c>
       <c r="P95">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q95">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R95">
         <v>0</v>
@@ -24597,7 +24597,7 @@
         <v>2.16</v>
       </c>
       <c r="W96">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X96">
         <v>1000</v>
@@ -25030,13 +25030,13 @@
         <v>375</v>
       </c>
       <c r="F98">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="G98">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="H98">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="I98">
         <v>2.02</v>
@@ -25051,91 +25051,91 @@
         <v>1.01</v>
       </c>
       <c r="M98">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N98">
-        <v>1.1</v>
+        <v>2.56</v>
       </c>
       <c r="O98">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P98">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="Q98">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="R98">
         <v>1.16</v>
       </c>
       <c r="S98">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T98">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="U98">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="V98">
         <v>1.98</v>
       </c>
       <c r="W98">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X98">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y98">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z98">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA98">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AB98">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC98">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD98">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE98">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF98">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG98">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AH98">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI98">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ98">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AK98">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AL98">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM98">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN98">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AO98">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP98">
         <v>1.03</v>
@@ -25189,7 +25189,7 @@
         <v>1.01</v>
       </c>
       <c r="BG98">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH98">
         <v>1000</v>
@@ -25272,13 +25272,13 @@
         <v>376</v>
       </c>
       <c r="F99">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G99">
         <v>1.88</v>
       </c>
       <c r="H99">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I99">
         <v>8.4</v>
@@ -25287,7 +25287,7 @@
         <v>3.15</v>
       </c>
       <c r="K99">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -25526,10 +25526,10 @@
         <v>8.4</v>
       </c>
       <c r="J100">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="K100">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -25768,7 +25768,7 @@
         <v>5</v>
       </c>
       <c r="J101">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="K101">
         <v>4.9</v>
@@ -25998,16 +25998,16 @@
         <v>379</v>
       </c>
       <c r="F102">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G102">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="H102">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I102">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J102">
         <v>3.45</v>
@@ -26482,10 +26482,10 @@
         <v>381</v>
       </c>
       <c r="F104">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G104">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="H104">
         <v>2.3</v>
@@ -26497,7 +26497,7 @@
         <v>2.72</v>
       </c>
       <c r="K104">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L104">
         <v>1.01</v>
@@ -26512,7 +26512,7 @@
         <v>1.36</v>
       </c>
       <c r="P104">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="Q104">
         <v>2.04</v>
@@ -26521,7 +26521,7 @@
         <v>1.17</v>
       </c>
       <c r="S104">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T104">
         <v>1.11</v>
@@ -26533,7 +26533,7 @@
         <v>1.41</v>
       </c>
       <c r="W104">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="X104">
         <v>1000</v>
@@ -26727,16 +26727,16 @@
         <v>1.77</v>
       </c>
       <c r="G105">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="H105">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="I105">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J105">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K105">
         <v>4.1</v>
@@ -26757,7 +26757,7 @@
         <v>1.96</v>
       </c>
       <c r="Q105">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -26966,19 +26966,19 @@
         <v>383</v>
       </c>
       <c r="F106">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G106">
         <v>2.32</v>
       </c>
       <c r="H106">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I106">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J106">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K106">
         <v>3.65</v>
@@ -26996,10 +26996,10 @@
         <v>0</v>
       </c>
       <c r="P106">
-        <v>1.07</v>
+        <v>1.8</v>
       </c>
       <c r="Q106">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -27220,7 +27220,7 @@
         <v>5.4</v>
       </c>
       <c r="J107">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K107">
         <v>3.7</v>
@@ -27238,10 +27238,10 @@
         <v>0</v>
       </c>
       <c r="P107">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q107">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -27698,28 +27698,28 @@
         <v>2.34</v>
       </c>
       <c r="H109">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I109">
         <v>3.75</v>
       </c>
       <c r="J109">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K109">
         <v>3.6</v>
       </c>
       <c r="L109">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M109">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N109">
         <v>3.3</v>
       </c>
       <c r="O109">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P109">
         <v>1.8</v>
@@ -27734,7 +27734,7 @@
         <v>3.8</v>
       </c>
       <c r="T109">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U109">
         <v>2.04</v>
@@ -27749,7 +27749,7 @@
         <v>15</v>
       </c>
       <c r="Y109">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z109">
         <v>30</v>
@@ -27773,7 +27773,7 @@
         <v>17.5</v>
       </c>
       <c r="AG109">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH109">
         <v>22</v>
@@ -27803,55 +27803,55 @@
         <v>11</v>
       </c>
       <c r="AQ109">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AR109">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS109">
+        <v>4.4</v>
+      </c>
+      <c r="AT109">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU109">
+        <v>3.1</v>
+      </c>
+      <c r="AV109">
+        <v>3.7</v>
+      </c>
+      <c r="AW109">
         <v>4.3</v>
       </c>
-      <c r="AT109">
-        <v>3.2</v>
-      </c>
-      <c r="AU109">
-        <v>3.05</v>
-      </c>
-      <c r="AV109">
-        <v>3.65</v>
-      </c>
-      <c r="AW109">
-        <v>4.2</v>
-      </c>
       <c r="AX109">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="AY109">
         <v>3.45</v>
       </c>
       <c r="AZ109">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BA109">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB109">
         <v>4.1</v>
       </c>
       <c r="BC109">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD109">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE109">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF109">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BG109">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH109">
         <v>1000</v>
@@ -27934,7 +27934,7 @@
         <v>387</v>
       </c>
       <c r="F110">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="G110">
         <v>990</v>
@@ -27943,10 +27943,10 @@
         <v>2.5</v>
       </c>
       <c r="I110">
-        <v>29</v>
+        <v>870</v>
       </c>
       <c r="J110">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="K110">
         <v>32</v>
@@ -27964,7 +27964,7 @@
         <v>1.41</v>
       </c>
       <c r="P110">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q110">
         <v>1.41</v>
@@ -29416,10 +29416,10 @@
         <v>0</v>
       </c>
       <c r="P116">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="Q116">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R116">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-26.xlsx
@@ -1210,7 +1210,7 @@
     <t>Independiente (Ecu)</t>
   </si>
   <si>
-    <t>2026-07-24 06:19:56</t>
+    <t>2026-07-24 08:37:27</t>
   </si>
 </sst>
 </file>
@@ -1822,7 +1822,7 @@
         <v>5</v>
       </c>
       <c r="L2">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M2">
         <v>1.04</v>
@@ -1837,19 +1837,19 @@
         <v>2.28</v>
       </c>
       <c r="Q2">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S2">
         <v>2.66</v>
       </c>
       <c r="T2">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U2">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V2">
         <v>1.15</v>
@@ -1867,7 +1867,7 @@
         <v>75</v>
       </c>
       <c r="AA2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AB2">
         <v>12</v>
@@ -1879,7 +1879,7 @@
         <v>32</v>
       </c>
       <c r="AE2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF2">
         <v>12</v>
@@ -1894,76 +1894,76 @@
         <v>95</v>
       </c>
       <c r="AJ2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK2">
         <v>19</v>
       </c>
       <c r="AL2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM2">
         <v>130</v>
       </c>
       <c r="AN2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AO2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ2">
         <v>18.5</v>
       </c>
       <c r="AR2">
+        <v>4.1</v>
+      </c>
+      <c r="AS2">
+        <v>4.3</v>
+      </c>
+      <c r="AT2">
+        <v>8.6</v>
+      </c>
+      <c r="AU2">
+        <v>9.4</v>
+      </c>
+      <c r="AV2">
+        <v>19</v>
+      </c>
+      <c r="AW2">
         <v>4.2</v>
-      </c>
-      <c r="AS2">
-        <v>4.5</v>
-      </c>
-      <c r="AT2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV2">
-        <v>18.5</v>
-      </c>
-      <c r="AW2">
-        <v>4.4</v>
       </c>
       <c r="AX2">
         <v>8.6</v>
       </c>
       <c r="AY2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2">
         <v>18</v>
       </c>
       <c r="BA2">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BB2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BC2">
         <v>11</v>
       </c>
       <c r="BD2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BE2">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BF2">
         <v>5.2</v>
       </c>
       <c r="BG2">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BH2">
         <v>4.2</v>
@@ -2070,7 +2070,7 @@
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>2.14</v>
+        <v>1.1</v>
       </c>
       <c r="O3">
         <v>1.23</v>
@@ -2345,79 +2345,79 @@
         <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Z4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA4">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AB4">
         <v>6.4</v>
       </c>
       <c r="AC4">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD4">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AE4">
         <v>170</v>
       </c>
       <c r="AF4">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AG4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH4">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AI4">
         <v>180</v>
       </c>
       <c r="AJ4">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AK4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AL4">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AM4">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AN4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO4">
         <v>310</v>
       </c>
       <c r="AP4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ4">
         <v>13.5</v>
       </c>
       <c r="AR4">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="AS4">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AT4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AU4">
         <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="AW4">
-        <v>8.6</v>
+        <v>5</v>
       </c>
       <c r="AX4">
         <v>7.6</v>
@@ -2426,10 +2426,10 @@
         <v>9</v>
       </c>
       <c r="AZ4">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="BA4">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="BB4">
         <v>15.5</v>
@@ -2438,16 +2438,16 @@
         <v>19.5</v>
       </c>
       <c r="BD4">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="BE4">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="BF4">
         <v>14.5</v>
       </c>
       <c r="BG4">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -2530,22 +2530,22 @@
         <v>283</v>
       </c>
       <c r="F5">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G5">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I5">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J5">
         <v>2.96</v>
       </c>
       <c r="K5">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2572,7 +2572,7 @@
         <v>7.2</v>
       </c>
       <c r="T5">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="U5">
         <v>1.55</v>
@@ -2581,7 +2581,7 @@
         <v>1.22</v>
       </c>
       <c r="W5">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -2641,7 +2641,7 @@
         <v>5.8</v>
       </c>
       <c r="AQ5">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR5">
         <v>6.6</v>
@@ -2650,7 +2650,7 @@
         <v>7.6</v>
       </c>
       <c r="AT5">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AU5">
         <v>5.8</v>
@@ -2817,7 +2817,7 @@
         <v>1.61</v>
       </c>
       <c r="U6">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V6">
         <v>1.98</v>
@@ -2877,10 +2877,10 @@
         <v>40</v>
       </c>
       <c r="AO6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ6">
         <v>11.5</v>
@@ -2895,7 +2895,7 @@
         <v>16.5</v>
       </c>
       <c r="AU6">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV6">
         <v>9.800000000000001</v>
@@ -2919,7 +2919,7 @@
         <v>34</v>
       </c>
       <c r="BC6">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="BD6">
         <v>32</v>
@@ -3041,7 +3041,7 @@
         <v>4.7</v>
       </c>
       <c r="O7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P7">
         <v>2.24</v>
@@ -3065,7 +3065,7 @@
         <v>1.23</v>
       </c>
       <c r="W7">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X7">
         <v>19</v>
@@ -3089,7 +3089,7 @@
         <v>20</v>
       </c>
       <c r="AE7">
-        <v>490</v>
+        <v>630</v>
       </c>
       <c r="AF7">
         <v>12</v>
@@ -3101,13 +3101,13 @@
         <v>18</v>
       </c>
       <c r="AI7">
-        <v>520</v>
+        <v>680</v>
       </c>
       <c r="AJ7">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL7">
         <v>32</v>
@@ -3125,7 +3125,7 @@
         <v>17</v>
       </c>
       <c r="AQ7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR7">
         <v>24</v>
@@ -3137,10 +3137,10 @@
         <v>9</v>
       </c>
       <c r="AU7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW7">
         <v>29</v>
@@ -3152,7 +3152,7 @@
         <v>9</v>
       </c>
       <c r="AZ7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA7">
         <v>30</v>
@@ -3179,19 +3179,19 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="BJ7">
         <v>13</v>
       </c>
       <c r="BK7">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="BN7">
         <v>6</v>
@@ -3203,22 +3203,22 @@
         <v>16</v>
       </c>
       <c r="BQ7">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="BR7">
         <v>34</v>
       </c>
       <c r="BS7">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="BT7">
         <v>11.5</v>
       </c>
       <c r="BU7">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="BV7">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
         <v>1.92</v>
@@ -3233,7 +3233,7 @@
         <v>25</v>
       </c>
       <c r="CA7">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CB7" t="s">
         <v>398</v>
@@ -3259,7 +3259,7 @@
         <v>2.1</v>
       </c>
       <c r="G8">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H8">
         <v>3.45</v>
@@ -3268,7 +3268,7 @@
         <v>3.65</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K8">
         <v>4.2</v>
@@ -3286,10 +3286,10 @@
         <v>1.2</v>
       </c>
       <c r="P8">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q8">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R8">
         <v>1.61</v>
@@ -3298,7 +3298,7 @@
         <v>2.54</v>
       </c>
       <c r="T8">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U8">
         <v>2.62</v>
@@ -3307,10 +3307,10 @@
         <v>1.37</v>
       </c>
       <c r="W8">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y8">
         <v>21</v>
@@ -3334,10 +3334,10 @@
         <v>65</v>
       </c>
       <c r="AF8">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH8">
         <v>17.5</v>
@@ -3355,7 +3355,7 @@
         <v>30</v>
       </c>
       <c r="AM8">
-        <v>580</v>
+        <v>470</v>
       </c>
       <c r="AN8">
         <v>11.5</v>
@@ -3364,7 +3364,7 @@
         <v>38</v>
       </c>
       <c r="AP8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ8">
         <v>16.5</v>
@@ -3376,7 +3376,7 @@
         <v>32</v>
       </c>
       <c r="AT8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU8">
         <v>8.6</v>
@@ -3388,7 +3388,7 @@
         <v>21</v>
       </c>
       <c r="AX8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY8">
         <v>9.800000000000001</v>
@@ -3421,7 +3421,7 @@
         <v>4.3</v>
       </c>
       <c r="BI8">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ8">
         <v>8.800000000000001</v>
@@ -3498,7 +3498,7 @@
         <v>287</v>
       </c>
       <c r="F9">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G9">
         <v>3.1</v>
@@ -3516,7 +3516,7 @@
         <v>3.85</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M9">
         <v>1.07</v>
@@ -3540,7 +3540,7 @@
         <v>3.3</v>
       </c>
       <c r="T9">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U9">
         <v>2.16</v>
@@ -3645,10 +3645,10 @@
         <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="BE9">
         <v>1.03</v>
@@ -3660,16 +3660,16 @@
         <v>17.5</v>
       </c>
       <c r="BH9">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="BI9">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -3678,46 +3678,46 @@
         <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="CB9" t="s">
         <v>398</v>
@@ -3740,22 +3740,22 @@
         <v>288</v>
       </c>
       <c r="F10">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G10">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="H10">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I10">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J10">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K10">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3782,16 +3782,16 @@
         <v>2.84</v>
       </c>
       <c r="T10">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V10">
         <v>1.23</v>
       </c>
       <c r="W10">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="X10">
         <v>23</v>
@@ -3997,16 +3997,16 @@
         <v>3.25</v>
       </c>
       <c r="K11">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N11">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O11">
         <v>1.25</v>
@@ -4018,16 +4018,16 @@
         <v>1.69</v>
       </c>
       <c r="R11">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S11">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="T11">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="V11">
         <v>1.42</v>
@@ -4036,91 +4036,91 @@
         <v>1.64</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP11">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ11">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR11">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AS11">
         <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AU11">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV11">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW11">
         <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY11">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ11">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA11">
         <v>1.03</v>
@@ -4129,7 +4129,7 @@
         <v>1.03</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BD11">
         <v>1.03</v>
@@ -4138,70 +4138,70 @@
         <v>1.03</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="CB11" t="s">
         <v>398</v>
@@ -4224,22 +4224,22 @@
         <v>290</v>
       </c>
       <c r="F12">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G12">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="H12">
         <v>4.1</v>
       </c>
       <c r="I12">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J12">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -4248,19 +4248,19 @@
         <v>1.1</v>
       </c>
       <c r="N12">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O12">
         <v>1.4</v>
       </c>
       <c r="P12">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q12">
         <v>2.22</v>
       </c>
       <c r="R12">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S12">
         <v>4.1</v>
@@ -4272,10 +4272,10 @@
         <v>1.98</v>
       </c>
       <c r="V12">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W12">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="X12">
         <v>11</v>
@@ -4284,37 +4284,37 @@
         <v>13.5</v>
       </c>
       <c r="Z12">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AA12">
         <v>110</v>
       </c>
       <c r="AB12">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD12">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE12">
         <v>60</v>
       </c>
       <c r="AF12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG12">
         <v>13.5</v>
       </c>
       <c r="AH12">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI12">
         <v>90</v>
       </c>
       <c r="AJ12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK12">
         <v>26</v>
@@ -4341,7 +4341,7 @@
         <v>21</v>
       </c>
       <c r="AS12">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT12">
         <v>7.6</v>
@@ -4353,10 +4353,10 @@
         <v>14.5</v>
       </c>
       <c r="AW12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY12">
         <v>9.800000000000001</v>
@@ -4365,7 +4365,7 @@
         <v>15.5</v>
       </c>
       <c r="BA12">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB12">
         <v>7.6</v>
@@ -4374,16 +4374,16 @@
         <v>21</v>
       </c>
       <c r="BD12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE12">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF12">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="BG12">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -4544,7 +4544,7 @@
         <v>32</v>
       </c>
       <c r="AF13">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG13">
         <v>12</v>
@@ -4732,7 +4732,7 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O14">
         <v>1.31</v>
@@ -5192,7 +5192,7 @@
         <v>294</v>
       </c>
       <c r="F16">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="G16">
         <v>1.29</v>
@@ -5222,7 +5222,7 @@
         <v>1.11</v>
       </c>
       <c r="P16">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q16">
         <v>1.35</v>
@@ -5240,7 +5240,7 @@
         <v>2.2</v>
       </c>
       <c r="V16">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W16">
         <v>4.5</v>
@@ -5261,10 +5261,10 @@
         <v>16</v>
       </c>
       <c r="AC16">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AD16">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AE16">
         <v>1000</v>
@@ -5276,7 +5276,7 @@
         <v>12</v>
       </c>
       <c r="AH16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI16">
         <v>110</v>
@@ -5348,70 +5348,70 @@
         <v>38</v>
       </c>
       <c r="BF16">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BG16">
         <v>42</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="CB16" t="s">
         <v>398</v>
@@ -5434,16 +5434,16 @@
         <v>295</v>
       </c>
       <c r="F17">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G17">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H17">
         <v>2.72</v>
       </c>
       <c r="I17">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -5464,13 +5464,13 @@
         <v>1.16</v>
       </c>
       <c r="P17">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q17">
         <v>1.49</v>
       </c>
       <c r="R17">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="S17">
         <v>2.22</v>
@@ -5479,10 +5479,10 @@
         <v>1.46</v>
       </c>
       <c r="U17">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="V17">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W17">
         <v>1.63</v>
@@ -5494,7 +5494,7 @@
         <v>26</v>
       </c>
       <c r="Z17">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA17">
         <v>110</v>
@@ -5506,7 +5506,7 @@
         <v>11</v>
       </c>
       <c r="AD17">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE17">
         <v>36</v>
@@ -5518,13 +5518,13 @@
         <v>13</v>
       </c>
       <c r="AH17">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI17">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ17">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK17">
         <v>32</v>
@@ -5554,7 +5554,7 @@
         <v>24</v>
       </c>
       <c r="AT17">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AU17">
         <v>9.4</v>
@@ -5563,7 +5563,7 @@
         <v>11.5</v>
       </c>
       <c r="AW17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AX17">
         <v>15.5</v>
@@ -5572,7 +5572,7 @@
         <v>11</v>
       </c>
       <c r="AZ17">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA17">
         <v>18.5</v>
@@ -5721,10 +5721,10 @@
         <v>1.5</v>
       </c>
       <c r="U18">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="V18">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
         <v>2.04</v>
@@ -6402,13 +6402,13 @@
         <v>299</v>
       </c>
       <c r="F21">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G21">
         <v>1.49</v>
       </c>
       <c r="H21">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I21">
         <v>8.4</v>
@@ -6417,7 +6417,7 @@
         <v>5.1</v>
       </c>
       <c r="K21">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -6435,13 +6435,13 @@
         <v>2.36</v>
       </c>
       <c r="Q21">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R21">
         <v>1.54</v>
       </c>
       <c r="S21">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T21">
         <v>1.83</v>
@@ -6459,7 +6459,7 @@
         <v>25</v>
       </c>
       <c r="Y21">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Z21">
         <v>70</v>
@@ -6474,7 +6474,7 @@
         <v>13</v>
       </c>
       <c r="AD21">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE21">
         <v>120</v>
@@ -6489,7 +6489,7 @@
         <v>24</v>
       </c>
       <c r="AI21">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AJ21">
         <v>13</v>
@@ -6516,10 +6516,10 @@
         <v>17.5</v>
       </c>
       <c r="AR21">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AS21">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AT21">
         <v>8.800000000000001</v>
@@ -6531,7 +6531,7 @@
         <v>17.5</v>
       </c>
       <c r="AW21">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AX21">
         <v>8.199999999999999</v>
@@ -6543,7 +6543,7 @@
         <v>20</v>
       </c>
       <c r="BA21">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB21">
         <v>11</v>
@@ -6555,13 +6555,13 @@
         <v>21</v>
       </c>
       <c r="BE21">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BF21">
         <v>5.2</v>
       </c>
       <c r="BG21">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -6656,7 +6656,7 @@
         <v>990</v>
       </c>
       <c r="J22">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K22">
         <v>500</v>
@@ -6668,22 +6668,22 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P22">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q22">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="R22">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S22">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="T22">
         <v>1.11</v>
@@ -6895,10 +6895,10 @@
         <v>1.04</v>
       </c>
       <c r="I23">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K23">
         <v>500</v>
@@ -6910,10 +6910,10 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P23">
         <v>1.24</v>
@@ -6922,10 +6922,10 @@
         <v>1.02</v>
       </c>
       <c r="R23">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S23">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="T23">
         <v>1.11</v>
@@ -7131,16 +7131,16 @@
         <v>1.04</v>
       </c>
       <c r="G24">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H24">
         <v>1.04</v>
       </c>
       <c r="I24">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K24">
         <v>500</v>
@@ -7152,28 +7152,28 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O24">
         <v>1.01</v>
       </c>
       <c r="P24">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R24">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S24">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="T24">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U24">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V24">
         <v>1.01</v>
@@ -7394,7 +7394,7 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="O25">
         <v>1.23</v>
@@ -7406,16 +7406,16 @@
         <v>1.68</v>
       </c>
       <c r="R25">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S25">
         <v>2.62</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V25">
         <v>1.43</v>
@@ -7615,22 +7615,22 @@
         <v>1.64</v>
       </c>
       <c r="G26">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H26">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="I26">
         <v>6.4</v>
       </c>
       <c r="J26">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K26">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="L26">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M26">
         <v>1.06</v>
@@ -7639,139 +7639,139 @@
         <v>3.65</v>
       </c>
       <c r="O26">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P26">
         <v>1.92</v>
       </c>
       <c r="Q26">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R26">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S26">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T26">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="U26">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V26">
         <v>1.18</v>
       </c>
       <c r="W26">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X26">
         <v>16</v>
       </c>
       <c r="Y26">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Z26">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA26">
         <v>180</v>
       </c>
       <c r="AB26">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC26">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD26">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE26">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF26">
         <v>11</v>
       </c>
       <c r="AG26">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI26">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ26">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK26">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL26">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM26">
         <v>140</v>
       </c>
       <c r="AN26">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AO26">
         <v>120</v>
       </c>
       <c r="AP26">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ26">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AR26">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="AS26">
         <v>1.03</v>
       </c>
       <c r="AT26">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU26">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV26">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AW26">
         <v>1.03</v>
       </c>
       <c r="AX26">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AY26">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ26">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA26">
         <v>1.03</v>
       </c>
       <c r="BB26">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BC26">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD26">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="BE26">
         <v>1.03</v>
       </c>
       <c r="BF26">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG26">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7872,208 +7872,208 @@
         <v>4.3</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P27">
         <v>1.95</v>
       </c>
       <c r="Q27">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH27">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BI27">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BJ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="s">
         <v>398</v>
@@ -8114,16 +8114,16 @@
         <v>6.4</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P28">
         <v>1.62</v>
@@ -8132,184 +8132,184 @@
         <v>1.96</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BI28">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
         <v>0</v>
@@ -8338,226 +8338,226 @@
         <v>307</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P29">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q29">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BD29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BE29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BF29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BH29">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BI29">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BJ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="s">
         <v>398</v>
@@ -8580,226 +8580,226 @@
         <v>308</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P30">
-        <v>1.07</v>
+        <v>1.64</v>
       </c>
       <c r="Q30">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AU30">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AV30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AX30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AY30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BA30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BD30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BE30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BF30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BH30">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BI30">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BJ30">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK30">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BO30">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BP30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BR30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BT30">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BU30">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BV30">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BW30">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BX30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BZ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA30">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="CB30" t="s">
         <v>398</v>
@@ -8822,226 +8822,226 @@
         <v>309</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P31">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="Q31">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BG31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ31">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB31" t="s">
         <v>398</v>
@@ -9064,226 +9064,226 @@
         <v>310</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P32">
-        <v>1.24</v>
+        <v>1.84</v>
       </c>
       <c r="Q32">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU32">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AW32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AX32">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AY32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BA32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BB32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BD32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BE32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BF32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BH32">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BI32">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BJ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="s">
         <v>398</v>
@@ -9551,223 +9551,223 @@
         <v>1.79</v>
       </c>
       <c r="G34">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="H34">
         <v>3.85</v>
       </c>
       <c r="I34">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J34">
         <v>4.4</v>
       </c>
       <c r="K34">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P34">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="Q34">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP34">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AU34">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV34">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW34">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AX34">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY34">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ34">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA34">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BB34">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BC34">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE34">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BF34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ34">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB34" t="s">
         <v>398</v>
@@ -9793,7 +9793,7 @@
         <v>3.55</v>
       </c>
       <c r="G35">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H35">
         <v>2.08</v>
@@ -9967,7 +9967,7 @@
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="BN35">
         <v>7.2</v>
@@ -10041,10 +10041,10 @@
         <v>6.2</v>
       </c>
       <c r="I36">
-        <v>990</v>
+        <v>9</v>
       </c>
       <c r="J36">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K36">
         <v>10.5</v>
@@ -10056,19 +10056,19 @@
         <v>1.01</v>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O36">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P36">
         <v>1.83</v>
       </c>
       <c r="Q36">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="R36">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S36">
         <v>2.5</v>
@@ -10080,7 +10080,7 @@
         <v>1.11</v>
       </c>
       <c r="V36">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W36">
         <v>2.5</v>
@@ -10770,7 +10770,7 @@
         <v>3.45</v>
       </c>
       <c r="J39">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K39">
         <v>4.6</v>
@@ -10788,7 +10788,7 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="Q39">
         <v>1.44</v>
@@ -11006,7 +11006,7 @@
         <v>2.16</v>
       </c>
       <c r="H40">
-        <v>1.89</v>
+        <v>3.25</v>
       </c>
       <c r="I40">
         <v>5</v>
@@ -11275,7 +11275,7 @@
         <v>2.82</v>
       </c>
       <c r="Q41">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -11484,13 +11484,13 @@
         <v>320</v>
       </c>
       <c r="F42">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G42">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="H42">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="I42">
         <v>1.5</v>
@@ -11499,7 +11499,7 @@
         <v>5.3</v>
       </c>
       <c r="K42">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -11732,7 +11732,7 @@
         <v>1.53</v>
       </c>
       <c r="H43">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I43">
         <v>7.2</v>
@@ -11741,7 +11741,7 @@
         <v>5</v>
       </c>
       <c r="K43">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -11756,7 +11756,7 @@
         <v>0</v>
       </c>
       <c r="P43">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q43">
         <v>1.48</v>
@@ -12452,7 +12452,7 @@
         <v>324</v>
       </c>
       <c r="F46">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="G46">
         <v>6.2</v>
@@ -12482,7 +12482,7 @@
         <v>0</v>
       </c>
       <c r="P46">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="Q46">
         <v>1.5</v>
@@ -12697,19 +12697,19 @@
         <v>2.66</v>
       </c>
       <c r="G47">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="H47">
         <v>2.6</v>
       </c>
       <c r="I47">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="J47">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K47">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -12724,7 +12724,7 @@
         <v>0</v>
       </c>
       <c r="P47">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q47">
         <v>1.87</v>
@@ -13178,7 +13178,7 @@
         <v>327</v>
       </c>
       <c r="F49">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G49">
         <v>2.5</v>
@@ -13187,7 +13187,7 @@
         <v>2.92</v>
       </c>
       <c r="I49">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J49">
         <v>3.8</v>
@@ -13423,16 +13423,16 @@
         <v>1.77</v>
       </c>
       <c r="G50">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="H50">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I50">
+        <v>4.6</v>
+      </c>
+      <c r="J50">
         <v>4.5</v>
-      </c>
-      <c r="J50">
-        <v>4.4</v>
       </c>
       <c r="K50">
         <v>4.8</v>
@@ -13450,7 +13450,7 @@
         <v>0</v>
       </c>
       <c r="P50">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Q50">
         <v>1.46</v>
@@ -13665,7 +13665,7 @@
         <v>2.1</v>
       </c>
       <c r="G51">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="H51">
         <v>3.1</v>
@@ -13674,7 +13674,7 @@
         <v>4.1</v>
       </c>
       <c r="J51">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="K51">
         <v>4.8</v>
@@ -13907,7 +13907,7 @@
         <v>1.59</v>
       </c>
       <c r="G52">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="H52">
         <v>6.4</v>
@@ -13922,13 +13922,13 @@
         <v>4.4</v>
       </c>
       <c r="L52">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M52">
         <v>1.07</v>
       </c>
       <c r="N52">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O52">
         <v>1.33</v>
@@ -13949,13 +13949,13 @@
         <v>1.97</v>
       </c>
       <c r="U52">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V52">
         <v>1.15</v>
       </c>
       <c r="W52">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="X52">
         <v>17.5</v>
@@ -13970,10 +13970,10 @@
         <v>240</v>
       </c>
       <c r="AB52">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC52">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD52">
         <v>27</v>
@@ -13982,7 +13982,7 @@
         <v>130</v>
       </c>
       <c r="AF52">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG52">
         <v>12</v>
@@ -13997,7 +13997,7 @@
         <v>16</v>
       </c>
       <c r="AK52">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL52">
         <v>42</v>
@@ -14018,22 +14018,22 @@
         <v>17.5</v>
       </c>
       <c r="AR52">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS52">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT52">
         <v>6.6</v>
       </c>
       <c r="AU52">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AV52">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AW52">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AX52">
         <v>7.8</v>
@@ -14045,7 +14045,7 @@
         <v>20</v>
       </c>
       <c r="BA52">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB52">
         <v>12.5</v>
@@ -14054,16 +14054,16 @@
         <v>15</v>
       </c>
       <c r="BD52">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="BE52">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF52">
-        <v>3.65</v>
+        <v>8.4</v>
       </c>
       <c r="BG52">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH52">
         <v>3.6</v>
@@ -14152,10 +14152,10 @@
         <v>1.23</v>
       </c>
       <c r="H53">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="I53">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J53">
         <v>7.4</v>
@@ -14630,7 +14630,7 @@
         <v>333</v>
       </c>
       <c r="F55">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G55">
         <v>6.2</v>
@@ -14639,7 +14639,7 @@
         <v>1.7</v>
       </c>
       <c r="I55">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J55">
         <v>3.95</v>
@@ -15598,7 +15598,7 @@
         <v>337</v>
       </c>
       <c r="F59">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G59">
         <v>1.45</v>
@@ -15607,13 +15607,13 @@
         <v>7.6</v>
       </c>
       <c r="I59">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J59">
         <v>5.4</v>
       </c>
       <c r="K59">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -16082,10 +16082,10 @@
         <v>339</v>
       </c>
       <c r="F61">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G61">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H61">
         <v>6.8</v>
@@ -16112,7 +16112,7 @@
         <v>0</v>
       </c>
       <c r="P61">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q61">
         <v>1.51</v>
@@ -16566,7 +16566,7 @@
         <v>341</v>
       </c>
       <c r="F63">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G63">
         <v>1.97</v>
@@ -16575,7 +16575,7 @@
         <v>4</v>
       </c>
       <c r="I63">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J63">
         <v>4</v>
@@ -16808,7 +16808,7 @@
         <v>342</v>
       </c>
       <c r="F64">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G64">
         <v>1.41</v>
@@ -16817,10 +16817,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I64">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J64">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K64">
         <v>5.6</v>
@@ -17292,7 +17292,7 @@
         <v>344</v>
       </c>
       <c r="F66">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G66">
         <v>1.76</v>
@@ -17612,10 +17612,10 @@
         <v>32</v>
       </c>
       <c r="AF67">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG67">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH67">
         <v>20</v>
@@ -17627,16 +17627,16 @@
         <v>65</v>
       </c>
       <c r="AK67">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL67">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM67">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN67">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO67">
         <v>23</v>
@@ -17651,7 +17651,7 @@
         <v>12</v>
       </c>
       <c r="AS67">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="AT67">
         <v>10</v>
@@ -17666,7 +17666,7 @@
         <v>18</v>
       </c>
       <c r="AX67">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AY67">
         <v>10</v>
@@ -17675,19 +17675,19 @@
         <v>12</v>
       </c>
       <c r="BA67">
+        <v>3.9</v>
+      </c>
+      <c r="BB67">
         <v>4</v>
       </c>
-      <c r="BB67">
+      <c r="BC67">
+        <v>3.9</v>
+      </c>
+      <c r="BD67">
+        <v>34</v>
+      </c>
+      <c r="BE67">
         <v>4.1</v>
-      </c>
-      <c r="BC67">
-        <v>4</v>
-      </c>
-      <c r="BD67">
-        <v>4.1</v>
-      </c>
-      <c r="BE67">
-        <v>4.2</v>
       </c>
       <c r="BF67">
         <v>21</v>
@@ -18021,16 +18021,16 @@
         <v>2.86</v>
       </c>
       <c r="G69">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="H69">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I69">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="J69">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K69">
         <v>4.1</v>
@@ -18048,7 +18048,7 @@
         <v>0</v>
       </c>
       <c r="P69">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q69">
         <v>1.77</v>
@@ -18260,16 +18260,16 @@
         <v>348</v>
       </c>
       <c r="F70">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="G70">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="H70">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="I70">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="J70">
         <v>5.4</v>
@@ -18502,22 +18502,22 @@
         <v>349</v>
       </c>
       <c r="F71">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G71">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H71">
-        <v>2.22</v>
+        <v>4.8</v>
       </c>
       <c r="I71">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="J71">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K71">
-        <v>500</v>
+        <v>5.1</v>
       </c>
       <c r="L71">
         <v>1.01</v>
@@ -18526,22 +18526,22 @@
         <v>1.01</v>
       </c>
       <c r="N71">
-        <v>2.88</v>
+        <v>6.4</v>
       </c>
       <c r="O71">
         <v>1.1</v>
       </c>
       <c r="P71">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="Q71">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R71">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="S71">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="T71">
         <v>1.11</v>
@@ -18550,7 +18550,7 @@
         <v>1.11</v>
       </c>
       <c r="V71">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="W71">
         <v>2.18</v>
@@ -18747,16 +18747,16 @@
         <v>3.15</v>
       </c>
       <c r="G72">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H72">
         <v>2.22</v>
       </c>
       <c r="I72">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="J72">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K72">
         <v>4.1</v>
@@ -19252,7 +19252,7 @@
         <v>1.02</v>
       </c>
       <c r="N74">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="O74">
         <v>1.15</v>
@@ -19261,13 +19261,13 @@
         <v>2.86</v>
       </c>
       <c r="Q74">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="R74">
         <v>1.73</v>
       </c>
       <c r="S74">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="T74">
         <v>1.46</v>
@@ -19712,7 +19712,7 @@
         <v>354</v>
       </c>
       <c r="F76">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G76">
         <v>2.2</v>
@@ -19721,13 +19721,13 @@
         <v>2.96</v>
       </c>
       <c r="I76">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J76">
         <v>4.4</v>
       </c>
       <c r="K76">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="L76">
         <v>1.01</v>
@@ -19742,37 +19742,37 @@
         <v>1.09</v>
       </c>
       <c r="P76">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q76">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R76">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S76">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="T76">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="U76">
         <v>3.35</v>
       </c>
       <c r="V76">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W76">
         <v>1.84</v>
       </c>
       <c r="X76">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Y76">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Z76">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA76">
         <v>60</v>
@@ -19781,67 +19781,67 @@
         <v>30</v>
       </c>
       <c r="AC76">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AD76">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE76">
         <v>34</v>
       </c>
       <c r="AF76">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG76">
         <v>14</v>
       </c>
       <c r="AH76">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI76">
         <v>32</v>
       </c>
       <c r="AJ76">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK76">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL76">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM76">
         <v>42</v>
       </c>
       <c r="AN76">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO76">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AP76">
         <v>1.03</v>
       </c>
       <c r="AQ76">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AR76">
         <v>20</v>
       </c>
       <c r="AS76">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="AT76">
         <v>21</v>
       </c>
       <c r="AU76">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV76">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW76">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AX76">
         <v>20</v>
@@ -19862,16 +19862,16 @@
         <v>16</v>
       </c>
       <c r="BD76">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BE76">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="BF76">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BG76">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH76">
         <v>1000</v>
@@ -20223,7 +20223,7 @@
         <v>6.2</v>
       </c>
       <c r="O78">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P78">
         <v>2.78</v>
@@ -20238,10 +20238,10 @@
         <v>2.16</v>
       </c>
       <c r="T78">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U78">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V78">
         <v>1.98</v>
@@ -20447,7 +20447,7 @@
         <v>2.98</v>
       </c>
       <c r="I79">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J79">
         <v>3.25</v>
@@ -20468,10 +20468,10 @@
         <v>0</v>
       </c>
       <c r="P79">
-        <v>1.07</v>
+        <v>1.94</v>
       </c>
       <c r="Q79">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -21164,22 +21164,22 @@
         <v>360</v>
       </c>
       <c r="F82">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G82">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H82">
         <v>5.4</v>
       </c>
       <c r="I82">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J82">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K82">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -21197,7 +21197,7 @@
         <v>1.69</v>
       </c>
       <c r="Q82">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -21221,7 +21221,7 @@
         <v>13.5</v>
       </c>
       <c r="Y82">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z82">
         <v>55</v>
@@ -21266,7 +21266,7 @@
         <v>210</v>
       </c>
       <c r="AN82">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO82">
         <v>180</v>
@@ -21412,7 +21412,7 @@
         <v>4.2</v>
       </c>
       <c r="H83">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="I83">
         <v>1.99</v>
@@ -21421,7 +21421,7 @@
         <v>3.9</v>
       </c>
       <c r="K83">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -21436,10 +21436,10 @@
         <v>0</v>
       </c>
       <c r="P83">
-        <v>1.1</v>
+        <v>2.24</v>
       </c>
       <c r="Q83">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -21681,13 +21681,13 @@
         <v>2.12</v>
       </c>
       <c r="Q84">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R84">
         <v>1.45</v>
       </c>
       <c r="S84">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T84">
         <v>1.63</v>
@@ -21920,7 +21920,7 @@
         <v>0</v>
       </c>
       <c r="P85">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q85">
         <v>1.01</v>
@@ -22132,23 +22132,23 @@
         <v>364</v>
       </c>
       <c r="F86">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="G86">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="H86">
+        <v>11</v>
+      </c>
+      <c r="I86">
+        <v>15</v>
+      </c>
+      <c r="J86">
+        <v>6.6</v>
+      </c>
+      <c r="K86">
         <v>8.800000000000001</v>
       </c>
-      <c r="I86">
-        <v>20</v>
-      </c>
-      <c r="J86">
-        <v>5.4</v>
-      </c>
-      <c r="K86">
-        <v>9.6</v>
-      </c>
       <c r="L86">
         <v>0</v>
       </c>
@@ -22162,10 +22162,10 @@
         <v>0</v>
       </c>
       <c r="P86">
-        <v>1.07</v>
+        <v>3.2</v>
       </c>
       <c r="Q86">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -22628,7 +22628,7 @@
         <v>1.54</v>
       </c>
       <c r="J88">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K88">
         <v>5.4</v>
@@ -22697,7 +22697,7 @@
         <v>70</v>
       </c>
       <c r="AG88">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH88">
         <v>18.5</v>
@@ -22748,7 +22748,7 @@
         <v>12</v>
       </c>
       <c r="AX88">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY88">
         <v>7.2</v>
@@ -22858,16 +22858,16 @@
         <v>367</v>
       </c>
       <c r="F89">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="G89">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="H89">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="I89">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="J89">
         <v>3.8</v>
@@ -22888,10 +22888,10 @@
         <v>0</v>
       </c>
       <c r="P89">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q89">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -23835,7 +23835,7 @@
         <v>2.9</v>
       </c>
       <c r="I93">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J93">
         <v>3.05</v>
@@ -23856,7 +23856,7 @@
         <v>0</v>
       </c>
       <c r="P93">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q93">
         <v>2.16</v>
@@ -24316,13 +24316,13 @@
         <v>1.83</v>
       </c>
       <c r="H95">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I95">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="J95">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K95">
         <v>5.5</v>
@@ -24552,22 +24552,22 @@
         <v>374</v>
       </c>
       <c r="F96">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G96">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H96">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="I96">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="J96">
         <v>3.3</v>
       </c>
       <c r="K96">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -24582,10 +24582,10 @@
         <v>0</v>
       </c>
       <c r="P96">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="Q96">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -24806,7 +24806,7 @@
         <v>1.85</v>
       </c>
       <c r="J97">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K97">
         <v>500</v>
@@ -24845,7 +24845,7 @@
         <v>2.16</v>
       </c>
       <c r="W97">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X97">
         <v>1000</v>
@@ -25278,13 +25278,13 @@
         <v>377</v>
       </c>
       <c r="F99">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="G99">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="H99">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="I99">
         <v>2.02</v>
@@ -25299,34 +25299,34 @@
         <v>1.01</v>
       </c>
       <c r="M99">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N99">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O99">
+        <v>1.51</v>
+      </c>
+      <c r="P99">
         <v>1.52</v>
       </c>
-      <c r="P99">
-        <v>1.56</v>
-      </c>
       <c r="Q99">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="R99">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S99">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T99">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U99">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V99">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="W99">
         <v>1.19</v>
@@ -25335,10 +25335,10 @@
         <v>11</v>
       </c>
       <c r="Y99">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z99">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AA99">
         <v>28</v>
@@ -25356,10 +25356,10 @@
         <v>34</v>
       </c>
       <c r="AF99">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG99">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH99">
         <v>34</v>
@@ -25368,73 +25368,73 @@
         <v>75</v>
       </c>
       <c r="AJ99">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AK99">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AL99">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AM99">
         <v>280</v>
       </c>
       <c r="AN99">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AO99">
         <v>28</v>
       </c>
       <c r="AP99">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AQ99">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AR99">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AS99">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AT99">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU99">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV99">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW99">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AX99">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY99">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AZ99">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BA99">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB99">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC99">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD99">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE99">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF99">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="BG99">
         <v>16.5</v>
@@ -25768,13 +25768,13 @@
         <v>2.1</v>
       </c>
       <c r="H101">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I101">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="J101">
-        <v>2.52</v>
+        <v>2.98</v>
       </c>
       <c r="K101">
         <v>3.5</v>
@@ -26972,19 +26972,19 @@
         <v>384</v>
       </c>
       <c r="F106">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G106">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H106">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I106">
         <v>5.5</v>
       </c>
       <c r="J106">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K106">
         <v>4.1</v>
@@ -27005,7 +27005,7 @@
         <v>2</v>
       </c>
       <c r="Q106">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -27226,7 +27226,7 @@
         <v>3.85</v>
       </c>
       <c r="J107">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K107">
         <v>3.65</v>
@@ -27489,7 +27489,7 @@
         <v>1.68</v>
       </c>
       <c r="Q108">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R108">
         <v>0</v>
@@ -27946,7 +27946,7 @@
         <v>2.34</v>
       </c>
       <c r="H110">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I110">
         <v>3.75</v>
@@ -27958,7 +27958,7 @@
         <v>3.6</v>
       </c>
       <c r="L110">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M110">
         <v>1.08</v>
@@ -27967,7 +27967,7 @@
         <v>3.3</v>
       </c>
       <c r="O110">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P110">
         <v>1.79</v>
@@ -27979,7 +27979,7 @@
         <v>1.3</v>
       </c>
       <c r="S110">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T110">
         <v>1.83</v>
@@ -27997,109 +27997,109 @@
         <v>15</v>
       </c>
       <c r="Y110">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z110">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AA110">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB110">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC110">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD110">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE110">
         <v>55</v>
       </c>
       <c r="AF110">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG110">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH110">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AI110">
+        <v>70</v>
+      </c>
+      <c r="AJ110">
+        <v>40</v>
+      </c>
+      <c r="AK110">
+        <v>34</v>
+      </c>
+      <c r="AL110">
+        <v>55</v>
+      </c>
+      <c r="AM110">
+        <v>140</v>
+      </c>
+      <c r="AN110">
+        <v>28</v>
+      </c>
+      <c r="AO110">
         <v>60</v>
       </c>
-      <c r="AJ110">
-        <v>38</v>
-      </c>
-      <c r="AK110">
-        <v>27</v>
-      </c>
-      <c r="AL110">
-        <v>44</v>
-      </c>
-      <c r="AM110">
-        <v>130</v>
-      </c>
-      <c r="AN110">
-        <v>23</v>
-      </c>
-      <c r="AO110">
-        <v>55</v>
-      </c>
       <c r="AP110">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ110">
+        <v>9</v>
+      </c>
+      <c r="AR110">
+        <v>17.5</v>
+      </c>
+      <c r="AS110">
+        <v>4</v>
+      </c>
+      <c r="AT110">
+        <v>6.8</v>
+      </c>
+      <c r="AU110">
+        <v>6</v>
+      </c>
+      <c r="AV110">
         <v>11</v>
       </c>
-      <c r="AQ110">
+      <c r="AW110">
+        <v>3.9</v>
+      </c>
+      <c r="AX110">
         <v>10.5</v>
       </c>
-      <c r="AR110">
-        <v>21</v>
-      </c>
-      <c r="AS110">
-        <v>5.7</v>
-      </c>
-      <c r="AT110">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU110">
-        <v>3.65</v>
-      </c>
-      <c r="AV110">
-        <v>13</v>
-      </c>
-      <c r="AW110">
-        <v>38</v>
-      </c>
-      <c r="AX110">
-        <v>12.5</v>
-      </c>
       <c r="AY110">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ110">
+        <v>13.5</v>
+      </c>
+      <c r="BA110">
+        <v>4</v>
+      </c>
+      <c r="BB110">
+        <v>3.8</v>
+      </c>
+      <c r="BC110">
+        <v>19.5</v>
+      </c>
+      <c r="BD110">
+        <v>30</v>
+      </c>
+      <c r="BE110">
+        <v>4.1</v>
+      </c>
+      <c r="BF110">
         <v>16</v>
       </c>
-      <c r="BA110">
-        <v>5.6</v>
-      </c>
-      <c r="BB110">
-        <v>5.3</v>
-      </c>
-      <c r="BC110">
-        <v>5</v>
-      </c>
-      <c r="BD110">
-        <v>36</v>
-      </c>
-      <c r="BE110">
-        <v>5.9</v>
-      </c>
-      <c r="BF110">
-        <v>4.8</v>
-      </c>
       <c r="BG110">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="BH110">
         <v>1000</v>
@@ -28182,7 +28182,7 @@
         <v>389</v>
       </c>
       <c r="F111">
-        <v>1.46</v>
+        <v>1.9</v>
       </c>
       <c r="G111">
         <v>990</v>
@@ -28194,10 +28194,10 @@
         <v>29</v>
       </c>
       <c r="J111">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="K111">
-        <v>32</v>
+        <v>3.95</v>
       </c>
       <c r="L111">
         <v>1.01</v>
@@ -28672,16 +28672,16 @@
         <v>990</v>
       </c>
       <c r="H113">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="I113">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="J113">
         <v>4.1</v>
       </c>
       <c r="K113">
-        <v>11.5</v>
+        <v>500</v>
       </c>
       <c r="L113">
         <v>1.01</v>
@@ -28690,7 +28690,7 @@
         <v>1.01</v>
       </c>
       <c r="N113">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O113">
         <v>1.23</v>
@@ -28714,7 +28714,7 @@
         <v>1.11</v>
       </c>
       <c r="V113">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="W113">
         <v>1.01</v>
@@ -29640,16 +29640,16 @@
         <v>2.36</v>
       </c>
       <c r="H117">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I117">
         <v>4.6</v>
       </c>
       <c r="J117">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K117">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L117">
         <v>0</v>
@@ -29664,10 +29664,10 @@
         <v>0</v>
       </c>
       <c r="P117">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q117">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="R117">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-26.xlsx
@@ -1279,7 +1279,7 @@
     <t>Independiente (Ecu)</t>
   </si>
   <si>
-    <t>2026-07-24 17:52:44</t>
+    <t>2026-07-24 20:10:57</t>
   </si>
 </sst>
 </file>
@@ -1885,13 +1885,13 @@
         <v>7.6</v>
       </c>
       <c r="J2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K2">
         <v>5</v>
       </c>
       <c r="L2">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M2">
         <v>1.04</v>
@@ -1924,7 +1924,7 @@
         <v>1.15</v>
       </c>
       <c r="W2">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="X2">
         <v>26</v>
@@ -2121,13 +2121,13 @@
         <v>1.33</v>
       </c>
       <c r="H3">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I3">
         <v>20</v>
       </c>
       <c r="J3">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="K3">
         <v>6.8</v>
@@ -2226,7 +2226,7 @@
         <v>15</v>
       </c>
       <c r="AQ3">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AR3">
         <v>1.03</v>
@@ -2250,7 +2250,7 @@
         <v>5.5</v>
       </c>
       <c r="AY3">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ3">
         <v>1.03</v>
@@ -2259,7 +2259,7 @@
         <v>1.03</v>
       </c>
       <c r="BB3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC3">
         <v>11</v>
@@ -2271,7 +2271,7 @@
         <v>1.03</v>
       </c>
       <c r="BF3">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BG3">
         <v>1.01</v>
@@ -2357,31 +2357,31 @@
         <v>296</v>
       </c>
       <c r="F4">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="G4">
         <v>1.78</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
         <v>7.6</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L4">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="M4">
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O4">
         <v>1.48</v>
@@ -2599,7 +2599,7 @@
         <v>297</v>
       </c>
       <c r="F5">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G5">
         <v>2.16</v>
@@ -2614,31 +2614,31 @@
         <v>2.98</v>
       </c>
       <c r="K5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L5">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="M5">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="N5">
         <v>2.22</v>
       </c>
       <c r="O5">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="P5">
         <v>1.39</v>
       </c>
       <c r="Q5">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R5">
         <v>1.13</v>
       </c>
       <c r="S5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="T5">
         <v>2.68</v>
@@ -2659,7 +2659,7 @@
         <v>11</v>
       </c>
       <c r="Z5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA5">
         <v>1000</v>
@@ -2680,7 +2680,7 @@
         <v>10.5</v>
       </c>
       <c r="AG5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH5">
         <v>38</v>
@@ -2692,10 +2692,10 @@
         <v>32</v>
       </c>
       <c r="AK5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL5">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
         <v>420</v>
@@ -2710,7 +2710,7 @@
         <v>6.2</v>
       </c>
       <c r="AQ5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5">
         <v>19.5</v>
@@ -2719,7 +2719,7 @@
         <v>42</v>
       </c>
       <c r="AT5">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AU5">
         <v>6.8</v>
@@ -2734,10 +2734,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AY5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BA5">
         <v>46</v>
@@ -2746,7 +2746,7 @@
         <v>18.5</v>
       </c>
       <c r="BC5">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BD5">
         <v>38</v>
@@ -2755,7 +2755,7 @@
         <v>55</v>
       </c>
       <c r="BF5">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BG5">
         <v>48</v>
@@ -2764,7 +2764,7 @@
         <v>2.48</v>
       </c>
       <c r="BI5">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BJ5">
         <v>14</v>
@@ -2853,13 +2853,13 @@
         <v>1.98</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K6">
         <v>4.2</v>
       </c>
       <c r="L6">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M6">
         <v>1.04</v>
@@ -2868,13 +2868,13 @@
         <v>5.3</v>
       </c>
       <c r="O6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
         <v>2.48</v>
       </c>
       <c r="Q6">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R6">
         <v>1.59</v>
@@ -2922,7 +2922,7 @@
         <v>34</v>
       </c>
       <c r="AG6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH6">
         <v>15.5</v>
@@ -2973,7 +2973,7 @@
         <v>16</v>
       </c>
       <c r="AX6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY6">
         <v>14</v>
@@ -3104,7 +3104,7 @@
         <v>1.37</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7">
         <v>4.3</v>
@@ -3113,19 +3113,19 @@
         <v>1.28</v>
       </c>
       <c r="P7">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q7">
         <v>1.87</v>
       </c>
       <c r="R7">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S7">
         <v>3.2</v>
       </c>
       <c r="T7">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U7">
         <v>2.14</v>
@@ -3149,7 +3149,7 @@
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC7">
         <v>8.6</v>
@@ -3176,7 +3176,7 @@
         <v>19</v>
       </c>
       <c r="AK7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL7">
         <v>34</v>
@@ -3185,7 +3185,7 @@
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO7">
         <v>1000</v>
@@ -3212,7 +3212,7 @@
         <v>17</v>
       </c>
       <c r="AW7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX7">
         <v>10</v>
@@ -3284,7 +3284,7 @@
         <v>11.5</v>
       </c>
       <c r="BU7">
-        <v>5.4</v>
+        <v>1.67</v>
       </c>
       <c r="BV7">
         <v>1000</v>
@@ -3328,7 +3328,7 @@
         <v>2.06</v>
       </c>
       <c r="G8">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H8">
         <v>3.55</v>
@@ -3352,7 +3352,7 @@
         <v>5.6</v>
       </c>
       <c r="O8">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P8">
         <v>2.54</v>
@@ -3376,7 +3376,7 @@
         <v>1.37</v>
       </c>
       <c r="W8">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X8">
         <v>26</v>
@@ -3400,7 +3400,7 @@
         <v>17</v>
       </c>
       <c r="AE8">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF8">
         <v>16</v>
@@ -3424,16 +3424,16 @@
         <v>30</v>
       </c>
       <c r="AM8">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AN8">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO8">
         <v>28</v>
       </c>
       <c r="AP8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ8">
         <v>17</v>
@@ -3469,7 +3469,7 @@
         <v>23</v>
       </c>
       <c r="BB8">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BC8">
         <v>17</v>
@@ -3487,7 +3487,7 @@
         <v>21</v>
       </c>
       <c r="BH8">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI8">
         <v>3.5</v>
@@ -3496,13 +3496,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK8">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN8">
         <v>5.3</v>
@@ -3514,13 +3514,13 @@
         <v>13.5</v>
       </c>
       <c r="BQ8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS8">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT8">
         <v>7.4</v>
@@ -3532,19 +3532,19 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX8">
         <v>32</v>
       </c>
       <c r="BY8">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB8" t="s">
         <v>421</v>
@@ -3615,7 +3615,7 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
         <v>1.68</v>
@@ -3809,25 +3809,25 @@
         <v>302</v>
       </c>
       <c r="F10">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G10">
         <v>3.05</v>
       </c>
       <c r="H10">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="I10">
         <v>2.9</v>
       </c>
       <c r="J10">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K10">
         <v>3.75</v>
       </c>
       <c r="L10">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M10">
         <v>1.07</v>
@@ -3845,7 +3845,7 @@
         <v>1.99</v>
       </c>
       <c r="R10">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
         <v>3.5</v>
@@ -3989,13 +3989,13 @@
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ10">
         <v>15.5</v>
@@ -4051,22 +4051,22 @@
         <v>303</v>
       </c>
       <c r="F11">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G11">
         <v>1.82</v>
       </c>
       <c r="H11">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I11">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J11">
         <v>4</v>
       </c>
       <c r="K11">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -4093,10 +4093,10 @@
         <v>2.8</v>
       </c>
       <c r="T11">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="U11">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="V11">
         <v>1.22</v>
@@ -4535,19 +4535,19 @@
         <v>305</v>
       </c>
       <c r="F13">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G13">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="H13">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="I13">
         <v>3.35</v>
       </c>
       <c r="J13">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K13">
         <v>4.2</v>
@@ -4577,7 +4577,7 @@
         <v>2.72</v>
       </c>
       <c r="T13">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U13">
         <v>2.32</v>
@@ -4586,7 +4586,7 @@
         <v>1.42</v>
       </c>
       <c r="W13">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="X13">
         <v>24</v>
@@ -4777,7 +4777,7 @@
         <v>306</v>
       </c>
       <c r="F14">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G14">
         <v>2.22</v>
@@ -4789,10 +4789,10 @@
         <v>4.4</v>
       </c>
       <c r="J14">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K14">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4807,7 +4807,7 @@
         <v>1.41</v>
       </c>
       <c r="P14">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Q14">
         <v>2.22</v>
@@ -5067,10 +5067,10 @@
         <v>3.05</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W15">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X15">
         <v>32</v>
@@ -5127,13 +5127,13 @@
         <v>15</v>
       </c>
       <c r="AP15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ15">
         <v>18.5</v>
       </c>
       <c r="AR15">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AS15">
         <v>26</v>
@@ -5261,16 +5261,16 @@
         <v>308</v>
       </c>
       <c r="F16">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="G16">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="H16">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="I16">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J16">
         <v>3.5</v>
@@ -5300,19 +5300,19 @@
         <v>1.31</v>
       </c>
       <c r="S16">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="T16">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="U16">
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W16">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -5509,7 +5509,7 @@
         <v>4.2</v>
       </c>
       <c r="H17">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I17">
         <v>2.6</v>
@@ -5518,7 +5518,7 @@
         <v>3.05</v>
       </c>
       <c r="K17">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -5745,7 +5745,7 @@
         <v>310</v>
       </c>
       <c r="F18">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="G18">
         <v>1.29</v>
@@ -5808,7 +5808,7 @@
         <v>1000</v>
       </c>
       <c r="AA18">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="AB18">
         <v>16</v>
@@ -5871,7 +5871,7 @@
         <v>16</v>
       </c>
       <c r="AV18">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AW18">
         <v>44</v>
@@ -5895,7 +5895,7 @@
         <v>11.5</v>
       </c>
       <c r="BD18">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE18">
         <v>38</v>
@@ -5987,13 +5987,13 @@
         <v>311</v>
       </c>
       <c r="F19">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G19">
         <v>2.58</v>
       </c>
       <c r="H19">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I19">
         <v>2.8</v>
@@ -6002,7 +6002,7 @@
         <v>4</v>
       </c>
       <c r="K19">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L19">
         <v>1.25</v>
@@ -6062,7 +6062,7 @@
         <v>13.5</v>
       </c>
       <c r="AE19">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AF19">
         <v>24</v>
@@ -6095,13 +6095,13 @@
         <v>13</v>
       </c>
       <c r="AP19">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ19">
         <v>17.5</v>
       </c>
       <c r="AR19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS19">
         <v>24</v>
@@ -6137,10 +6137,10 @@
         <v>19</v>
       </c>
       <c r="BD19">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BE19">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BF19">
         <v>10</v>
@@ -6164,7 +6164,7 @@
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN19">
         <v>6.2</v>
@@ -6179,10 +6179,10 @@
         <v>7.6</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS19">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT19">
         <v>6.6</v>
@@ -6191,13 +6191,13 @@
         <v>5.1</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW19">
         <v>7.8</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY19">
         <v>8.800000000000001</v>
@@ -6206,7 +6206,7 @@
         <v>13.5</v>
       </c>
       <c r="CA19">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB19" t="s">
         <v>421</v>
@@ -6229,10 +6229,10 @@
         <v>312</v>
       </c>
       <c r="F20">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="G20">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H20">
         <v>3.85</v>
@@ -6250,7 +6250,7 @@
         <v>1.24</v>
       </c>
       <c r="M20">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N20">
         <v>6.8</v>
@@ -6274,7 +6274,7 @@
         <v>1.5</v>
       </c>
       <c r="U20">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
         <v>1.33</v>
@@ -6358,7 +6358,7 @@
         <v>15</v>
       </c>
       <c r="AW20">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX20">
         <v>14</v>
@@ -6367,7 +6367,7 @@
         <v>10</v>
       </c>
       <c r="AZ20">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA20">
         <v>22</v>
@@ -6731,7 +6731,7 @@
         <v>3.75</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="M22">
         <v>1.07</v>
@@ -6758,7 +6758,7 @@
         <v>1.73</v>
       </c>
       <c r="U22">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V22">
         <v>1.52</v>
@@ -6970,7 +6970,7 @@
         <v>5.1</v>
       </c>
       <c r="K23">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6988,7 +6988,7 @@
         <v>2.36</v>
       </c>
       <c r="Q23">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R23">
         <v>1.55</v>
@@ -7138,7 +7138,7 @@
         <v>5.4</v>
       </c>
       <c r="BO23">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP23">
         <v>11.5</v>
@@ -7947,10 +7947,10 @@
         <v>1.01</v>
       </c>
       <c r="N27">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P27">
         <v>1.25</v>
@@ -8416,10 +8416,10 @@
         <v>5.4</v>
       </c>
       <c r="I29">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J29">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K29">
         <v>4.3</v>
@@ -8455,7 +8455,7 @@
         <v>1.11</v>
       </c>
       <c r="V29">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W29">
         <v>2.26</v>
@@ -8649,13 +8649,13 @@
         <v>322</v>
       </c>
       <c r="F30">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="G30">
         <v>2.1</v>
       </c>
       <c r="H30">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="I30">
         <v>5.6</v>
@@ -8664,7 +8664,7 @@
         <v>3.4</v>
       </c>
       <c r="K30">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8673,7 +8673,7 @@
         <v>1.01</v>
       </c>
       <c r="N30">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="O30">
         <v>1.35</v>
@@ -8682,7 +8682,7 @@
         <v>1.62</v>
       </c>
       <c r="Q30">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="R30">
         <v>1.22</v>
@@ -8900,13 +8900,13 @@
         <v>1.97</v>
       </c>
       <c r="I31">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J31">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K31">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8915,7 +8915,7 @@
         <v>1.06</v>
       </c>
       <c r="N31">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="O31">
         <v>1.48</v>
@@ -8933,7 +8933,7 @@
         <v>4</v>
       </c>
       <c r="T31">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U31">
         <v>1.71</v>
@@ -8951,7 +8951,7 @@
         <v>970</v>
       </c>
       <c r="Z31">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA31">
         <v>1000</v>
@@ -8963,7 +8963,7 @@
         <v>970</v>
       </c>
       <c r="AD31">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE31">
         <v>1000</v>
@@ -8999,58 +8999,58 @@
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AQ31">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR31">
-        <v>1.17</v>
+        <v>6.2</v>
       </c>
       <c r="AS31">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AT31">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AU31">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AV31">
-        <v>1.17</v>
+        <v>6.6</v>
       </c>
       <c r="AW31">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AX31">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AY31">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AZ31">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="BA31">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="BB31">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="BC31">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="BD31">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="BE31">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="BF31">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="BG31">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="BH31">
         <v>3.4</v>
@@ -9157,7 +9157,7 @@
         <v>1.06</v>
       </c>
       <c r="N32">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O32">
         <v>1.29</v>
@@ -9184,7 +9184,7 @@
         <v>1.23</v>
       </c>
       <c r="W32">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X32">
         <v>19</v>
@@ -9381,55 +9381,55 @@
         <v>1.84</v>
       </c>
       <c r="H33">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I33">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J33">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K33">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L33">
         <v>1.48</v>
       </c>
       <c r="M33">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N33">
         <v>2.7</v>
       </c>
       <c r="O33">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P33">
         <v>1.52</v>
       </c>
       <c r="Q33">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="R33">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S33">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="T33">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="U33">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V33">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W33">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X33">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y33">
         <v>1000</v>
@@ -9441,10 +9441,10 @@
         <v>1000</v>
       </c>
       <c r="AB33">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC33">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD33">
         <v>1000</v>
@@ -9453,10 +9453,10 @@
         <v>1000</v>
       </c>
       <c r="AF33">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG33">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH33">
         <v>1000</v>
@@ -9483,58 +9483,58 @@
         <v>1000</v>
       </c>
       <c r="AP33">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="AQ33">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AR33">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AS33">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AT33">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AU33">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="AV33">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AW33">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AX33">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="AY33">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="AZ33">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BA33">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BB33">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BC33">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BD33">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BE33">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BF33">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BG33">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -9620,7 +9620,7 @@
         <v>1.78</v>
       </c>
       <c r="G34">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H34">
         <v>3.75</v>
@@ -9635,16 +9635,16 @@
         <v>4.8</v>
       </c>
       <c r="L34">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="M34">
         <v>1.02</v>
       </c>
       <c r="N34">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="O34">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P34">
         <v>1.89</v>
@@ -9653,22 +9653,22 @@
         <v>1.88</v>
       </c>
       <c r="R34">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S34">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T34">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="U34">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="V34">
         <v>1.23</v>
       </c>
       <c r="W34">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X34">
         <v>1000</v>
@@ -9695,7 +9695,7 @@
         <v>1000</v>
       </c>
       <c r="AF34">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AG34">
         <v>21</v>
@@ -9719,64 +9719,64 @@
         <v>1000</v>
       </c>
       <c r="AN34">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO34">
         <v>1000</v>
       </c>
       <c r="AP34">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AQ34">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AR34">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AS34">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AT34">
-        <v>1.19</v>
+        <v>7</v>
       </c>
       <c r="AU34">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="AV34">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AW34">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AX34">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AY34">
-        <v>1.2</v>
+        <v>7.4</v>
       </c>
       <c r="AZ34">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="BA34">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="BB34">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="BC34">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="BD34">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="BE34">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="BF34">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BG34">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="BH34">
         <v>4.3</v>
@@ -9862,85 +9862,85 @@
         <v>4.4</v>
       </c>
       <c r="G35">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I35">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="J35">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K35">
         <v>3.45</v>
       </c>
       <c r="L35">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M35">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N35">
         <v>2.84</v>
       </c>
       <c r="O35">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P35">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q35">
         <v>2.42</v>
       </c>
       <c r="R35">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S35">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T35">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="U35">
         <v>1.76</v>
       </c>
       <c r="V35">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="W35">
         <v>1.26</v>
       </c>
       <c r="X35">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y35">
         <v>7.2</v>
       </c>
       <c r="Z35">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AA35">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB35">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC35">
         <v>7.6</v>
       </c>
       <c r="AD35">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE35">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF35">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG35">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH35">
         <v>28</v>
@@ -9949,22 +9949,22 @@
         <v>65</v>
       </c>
       <c r="AJ35">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AK35">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AL35">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM35">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN35">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AO35">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP35">
         <v>8.800000000000001</v>
@@ -9976,7 +9976,7 @@
         <v>10</v>
       </c>
       <c r="AS35">
-        <v>4.8</v>
+        <v>16.5</v>
       </c>
       <c r="AT35">
         <v>11</v>
@@ -9985,40 +9985,40 @@
         <v>6.8</v>
       </c>
       <c r="AV35">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW35">
-        <v>4.8</v>
+        <v>17.5</v>
       </c>
       <c r="AX35">
-        <v>4.9</v>
+        <v>19</v>
       </c>
       <c r="AY35">
         <v>17</v>
       </c>
       <c r="AZ35">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="BA35">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="BB35">
-        <v>5.2</v>
+        <v>38</v>
       </c>
       <c r="BC35">
-        <v>5.1</v>
+        <v>32</v>
       </c>
       <c r="BD35">
-        <v>5.2</v>
+        <v>38</v>
       </c>
       <c r="BE35">
-        <v>5.3</v>
+        <v>46</v>
       </c>
       <c r="BF35">
-        <v>5.2</v>
+        <v>38</v>
       </c>
       <c r="BG35">
-        <v>4.7</v>
+        <v>17</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -10343,7 +10343,7 @@
         <v>329</v>
       </c>
       <c r="F37">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G37">
         <v>1.87</v>
@@ -10352,7 +10352,7 @@
         <v>3.7</v>
       </c>
       <c r="I37">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J37">
         <v>4.4</v>
@@ -10376,19 +10376,19 @@
         <v>3.1</v>
       </c>
       <c r="Q37">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R37">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S37">
         <v>1.95</v>
       </c>
       <c r="T37">
+        <v>1.19</v>
+      </c>
+      <c r="U37">
         <v>1.11</v>
-      </c>
-      <c r="U37">
-        <v>2.84</v>
       </c>
       <c r="V37">
         <v>1.27</v>
@@ -10594,10 +10594,10 @@
         <v>2.08</v>
       </c>
       <c r="I38">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J38">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K38">
         <v>3.95</v>
@@ -10618,16 +10618,16 @@
         <v>2.2</v>
       </c>
       <c r="Q38">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R38">
         <v>1.47</v>
       </c>
       <c r="S38">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T38">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U38">
         <v>2.34</v>
@@ -10953,19 +10953,19 @@
         <v>8</v>
       </c>
       <c r="AV39">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AW39">
         <v>6.8</v>
       </c>
       <c r="AX39">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="AY39">
         <v>7.8</v>
       </c>
       <c r="AZ39">
-        <v>5.8</v>
+        <v>19</v>
       </c>
       <c r="BA39">
         <v>6.8</v>
@@ -10977,7 +10977,7 @@
         <v>13</v>
       </c>
       <c r="BD39">
-        <v>6.8</v>
+        <v>26</v>
       </c>
       <c r="BE39">
         <v>7</v>
@@ -11093,10 +11093,10 @@
         <v>1.01</v>
       </c>
       <c r="N40">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P40">
         <v>1.25</v>
@@ -11335,13 +11335,13 @@
         <v>1.01</v>
       </c>
       <c r="N41">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O41">
         <v>1.02</v>
       </c>
       <c r="P41">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q41">
         <v>1.46</v>
@@ -11598,7 +11598,7 @@
         <v>1.46</v>
       </c>
       <c r="U42">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="V42">
         <v>1.4</v>
@@ -11837,7 +11837,7 @@
         <v>2.34</v>
       </c>
       <c r="T43">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="U43">
         <v>2.42</v>
@@ -12127,7 +12127,7 @@
         <v>38</v>
       </c>
       <c r="AJ44">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK44">
         <v>20</v>
@@ -12166,10 +12166,10 @@
         <v>14.5</v>
       </c>
       <c r="AW44">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX44">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY44">
         <v>10</v>
@@ -12178,7 +12178,7 @@
         <v>13.5</v>
       </c>
       <c r="BA44">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB44">
         <v>20</v>
@@ -12282,7 +12282,7 @@
         <v>7</v>
       </c>
       <c r="G45">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H45">
         <v>1.48</v>
@@ -12372,7 +12372,7 @@
         <v>210</v>
       </c>
       <c r="AK45">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AL45">
         <v>75</v>
@@ -12429,7 +12429,7 @@
         <v>8.6</v>
       </c>
       <c r="BD45">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE45">
         <v>8.6</v>
@@ -12521,82 +12521,82 @@
         <v>338</v>
       </c>
       <c r="F46">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G46">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="H46">
+        <v>6.8</v>
+      </c>
+      <c r="I46">
         <v>7</v>
       </c>
-      <c r="I46">
-        <v>7.4</v>
-      </c>
       <c r="J46">
+        <v>5</v>
+      </c>
+      <c r="K46">
         <v>5.1</v>
       </c>
-      <c r="K46">
-        <v>5.2</v>
-      </c>
       <c r="L46">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M46">
         <v>1.02</v>
       </c>
       <c r="N46">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="O46">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P46">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="Q46">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R46">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="S46">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="T46">
         <v>1.64</v>
       </c>
       <c r="U46">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V46">
         <v>1.16</v>
       </c>
       <c r="W46">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="X46">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y46">
         <v>40</v>
       </c>
       <c r="Z46">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA46">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB46">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC46">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD46">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE46">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF46">
         <v>13.5</v>
@@ -12605,31 +12605,31 @@
         <v>10.5</v>
       </c>
       <c r="AH46">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI46">
         <v>65</v>
       </c>
       <c r="AJ46">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AK46">
         <v>14</v>
       </c>
       <c r="AL46">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM46">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AN46">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AO46">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP46">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AQ46">
         <v>30</v>
@@ -12638,10 +12638,10 @@
         <v>55</v>
       </c>
       <c r="AS46">
+        <v>11.5</v>
+      </c>
+      <c r="AT46">
         <v>12</v>
-      </c>
-      <c r="AT46">
-        <v>12.5</v>
       </c>
       <c r="AU46">
         <v>10.5</v>
@@ -12656,7 +12656,7 @@
         <v>10.5</v>
       </c>
       <c r="AY46">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ46">
         <v>16.5</v>
@@ -12677,7 +12677,7 @@
         <v>55</v>
       </c>
       <c r="BF46">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BG46">
         <v>46</v>
@@ -12686,19 +12686,19 @@
         <v>1000</v>
       </c>
       <c r="BI46">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BJ46">
         <v>13.5</v>
       </c>
       <c r="BK46">
-        <v>5.9</v>
+        <v>1.58</v>
       </c>
       <c r="BL46">
         <v>1000</v>
       </c>
       <c r="BM46">
-        <v>21</v>
+        <v>1.79</v>
       </c>
       <c r="BN46">
         <v>6.4</v>
@@ -12710,37 +12710,37 @@
         <v>13</v>
       </c>
       <c r="BQ46">
-        <v>5.6</v>
+        <v>1.57</v>
       </c>
       <c r="BR46">
         <v>28</v>
       </c>
       <c r="BS46">
-        <v>11.5</v>
+        <v>1.68</v>
       </c>
       <c r="BT46">
         <v>15</v>
       </c>
       <c r="BU46">
-        <v>6.4</v>
+        <v>1.6</v>
       </c>
       <c r="BV46">
         <v>1000</v>
       </c>
       <c r="BW46">
-        <v>21</v>
+        <v>1.74</v>
       </c>
       <c r="BX46">
         <v>1000</v>
       </c>
       <c r="BY46">
-        <v>21</v>
+        <v>1.74</v>
       </c>
       <c r="BZ46">
         <v>1000</v>
       </c>
       <c r="CA46">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="CB46" t="s">
         <v>421</v>
@@ -12808,7 +12808,7 @@
         <v>1.58</v>
       </c>
       <c r="U47">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V47">
         <v>1.47</v>
@@ -12943,28 +12943,28 @@
         <v>21</v>
       </c>
       <c r="BN47">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO47">
         <v>3.7</v>
       </c>
       <c r="BP47">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ47">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BR47">
         <v>38</v>
       </c>
       <c r="BS47">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BT47">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU47">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV47">
         <v>30</v>
@@ -13256,7 +13256,7 @@
         <v>1.65</v>
       </c>
       <c r="I49">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="J49">
         <v>4.6</v>
@@ -13289,7 +13289,7 @@
         <v>2.24</v>
       </c>
       <c r="T49">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="U49">
         <v>2.38</v>
@@ -13298,7 +13298,7 @@
         <v>2.5</v>
       </c>
       <c r="W49">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X49">
         <v>28</v>
@@ -13379,7 +13379,7 @@
         <v>13.5</v>
       </c>
       <c r="AX49">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY49">
         <v>19</v>
@@ -13439,16 +13439,16 @@
         <v>21</v>
       </c>
       <c r="BR49">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS49">
         <v>21</v>
       </c>
       <c r="BT49">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU49">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BV49">
         <v>13.5</v>
@@ -13457,16 +13457,16 @@
         <v>6.4</v>
       </c>
       <c r="BX49">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BY49">
         <v>12</v>
       </c>
       <c r="BZ49">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA49">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB49" t="s">
         <v>421</v>
@@ -13492,7 +13492,7 @@
         <v>2.52</v>
       </c>
       <c r="G50">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H50">
         <v>2.68</v>
@@ -14015,7 +14015,7 @@
         <v>3.05</v>
       </c>
       <c r="T52">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="U52">
         <v>2.12</v>
@@ -14045,7 +14045,7 @@
         <v>9.4</v>
       </c>
       <c r="AD52">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE52">
         <v>60</v>
@@ -14123,7 +14123,7 @@
         <v>16.5</v>
       </c>
       <c r="BD52">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE52">
         <v>8.6</v>
@@ -14144,7 +14144,7 @@
         <v>13.5</v>
       </c>
       <c r="BK52">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BL52">
         <v>1000</v>
@@ -14168,7 +14168,7 @@
         <v>36</v>
       </c>
       <c r="BS52">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BT52">
         <v>12</v>
@@ -14215,7 +14215,7 @@
         <v>345</v>
       </c>
       <c r="F53">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G53">
         <v>1.79</v>
@@ -14224,13 +14224,13 @@
         <v>4.4</v>
       </c>
       <c r="I53">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J53">
         <v>4.6</v>
       </c>
       <c r="K53">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L53">
         <v>1.01</v>
@@ -14263,7 +14263,7 @@
         <v>2.68</v>
       </c>
       <c r="V53">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W53">
         <v>2.26</v>
@@ -14275,7 +14275,7 @@
         <v>28</v>
       </c>
       <c r="Z53">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AA53">
         <v>85</v>
@@ -14284,13 +14284,13 @@
         <v>15.5</v>
       </c>
       <c r="AC53">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD53">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE53">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF53">
         <v>15</v>
@@ -14466,7 +14466,7 @@
         <v>3</v>
       </c>
       <c r="I54">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J54">
         <v>3.6</v>
@@ -14481,7 +14481,7 @@
         <v>1.05</v>
       </c>
       <c r="N54">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O54">
         <v>1.23</v>
@@ -14493,13 +14493,13 @@
         <v>1.67</v>
       </c>
       <c r="R54">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S54">
         <v>2.7</v>
       </c>
       <c r="T54">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="U54">
         <v>2.34</v>
@@ -14708,10 +14708,10 @@
         <v>6.4</v>
       </c>
       <c r="I55">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J55">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K55">
         <v>4.6</v>
@@ -14974,7 +14974,7 @@
         <v>2.46</v>
       </c>
       <c r="Q56">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R56">
         <v>1.59</v>
@@ -14983,10 +14983,10 @@
         <v>2.48</v>
       </c>
       <c r="T56">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="U56">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V56">
         <v>1.35</v>
@@ -15049,7 +15049,7 @@
         <v>32</v>
       </c>
       <c r="AP56">
-        <v>20</v>
+        <v>5.1</v>
       </c>
       <c r="AQ56">
         <v>16</v>
@@ -15183,58 +15183,58 @@
         <v>349</v>
       </c>
       <c r="F57">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="G57">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="H57">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I57">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J57">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K57">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L57">
         <v>1.01</v>
       </c>
       <c r="M57">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N57">
         <v>6</v>
       </c>
       <c r="O57">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P57">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q57">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="R57">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S57">
         <v>2.22</v>
       </c>
       <c r="T57">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="U57">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V57">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W57">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="X57">
         <v>32</v>
@@ -15243,7 +15243,7 @@
         <v>75</v>
       </c>
       <c r="Z57">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AA57">
         <v>1000</v>
@@ -15255,10 +15255,10 @@
         <v>21</v>
       </c>
       <c r="AD57">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AE57">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="AF57">
         <v>9</v>
@@ -15270,7 +15270,7 @@
         <v>48</v>
       </c>
       <c r="AI57">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="AJ57">
         <v>8.800000000000001</v>
@@ -15282,67 +15282,67 @@
         <v>55</v>
       </c>
       <c r="AM57">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="AN57">
         <v>3.65</v>
       </c>
       <c r="AO57">
-        <v>610</v>
+        <v>1000</v>
       </c>
       <c r="AP57">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ57">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR57">
+        <v>7</v>
+      </c>
+      <c r="AS57">
         <v>7.2</v>
       </c>
-      <c r="AS57">
-        <v>7.4</v>
-      </c>
       <c r="AT57">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="AU57">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AV57">
         <v>6.8</v>
       </c>
       <c r="AW57">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX57">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="AY57">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="AZ57">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA57">
         <v>7.2</v>
       </c>
       <c r="BB57">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC57">
-        <v>12.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD57">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE57">
+        <v>7</v>
+      </c>
+      <c r="BF57">
+        <v>3.15</v>
+      </c>
+      <c r="BG57">
         <v>7.2</v>
-      </c>
-      <c r="BF57">
-        <v>3.25</v>
-      </c>
-      <c r="BG57">
-        <v>7.4</v>
       </c>
       <c r="BH57">
         <v>1000</v>
@@ -15354,7 +15354,7 @@
         <v>20</v>
       </c>
       <c r="BK57">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL57">
         <v>1000</v>
@@ -15366,13 +15366,13 @@
         <v>4.9</v>
       </c>
       <c r="BO57">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BP57">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ57">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BR57">
         <v>32</v>
@@ -15381,10 +15381,10 @@
         <v>14.5</v>
       </c>
       <c r="BT57">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BU57">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BV57">
         <v>1000</v>
@@ -15399,7 +15399,7 @@
         <v>21</v>
       </c>
       <c r="BZ57">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA57">
         <v>5.4</v>
@@ -15694,13 +15694,13 @@
         <v>1.18</v>
       </c>
       <c r="O59">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="P59">
         <v>1.18</v>
       </c>
       <c r="Q59">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="R59">
         <v>1.18</v>
@@ -15918,7 +15918,7 @@
         <v>8</v>
       </c>
       <c r="I60">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J60">
         <v>5.4</v>
@@ -16181,7 +16181,7 @@
         <v>1.18</v>
       </c>
       <c r="P61">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q61">
         <v>1.52</v>
@@ -16253,7 +16253,7 @@
         <v>110</v>
       </c>
       <c r="AN61">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO61">
         <v>85</v>
@@ -16268,7 +16268,7 @@
         <v>55</v>
       </c>
       <c r="AS61">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT61">
         <v>10</v>
@@ -16334,13 +16334,13 @@
         <v>6</v>
       </c>
       <c r="BO61">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BP61">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ61">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR61">
         <v>29</v>
@@ -16405,7 +16405,7 @@
         <v>990</v>
       </c>
       <c r="J62">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K62">
         <v>500</v>
@@ -16647,7 +16647,7 @@
         <v>990</v>
       </c>
       <c r="J63">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="K63">
         <v>550</v>
@@ -16889,7 +16889,7 @@
         <v>990</v>
       </c>
       <c r="J64">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K64">
         <v>500</v>
@@ -17164,7 +17164,7 @@
         <v>1.56</v>
       </c>
       <c r="U65">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="V65">
         <v>1.25</v>
@@ -17287,58 +17287,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ65">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK65">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL65">
         <v>1000</v>
       </c>
       <c r="BM65">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN65">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO65">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP65">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ65">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR65">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS65">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT65">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU65">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV65">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW65">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX65">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY65">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BZ65">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="CA65">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB65" t="s">
         <v>421</v>
@@ -17403,7 +17403,7 @@
         <v>2.34</v>
       </c>
       <c r="T66">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="U66">
         <v>2.26</v>
@@ -17508,10 +17508,10 @@
         <v>12.5</v>
       </c>
       <c r="BC66">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BD66">
-        <v>4.9</v>
+        <v>20</v>
       </c>
       <c r="BE66">
         <v>5.4</v>
@@ -17645,10 +17645,10 @@
         <v>3.75</v>
       </c>
       <c r="T67">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="U67">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="V67">
         <v>1.57</v>
@@ -17660,7 +17660,7 @@
         <v>13</v>
       </c>
       <c r="Y67">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z67">
         <v>17</v>
@@ -17672,7 +17672,7 @@
         <v>12</v>
       </c>
       <c r="AC67">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD67">
         <v>14</v>
@@ -17687,7 +17687,7 @@
         <v>14.5</v>
       </c>
       <c r="AH67">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI67">
         <v>65</v>
@@ -17714,25 +17714,25 @@
         <v>9.6</v>
       </c>
       <c r="AQ67">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR67">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS67">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT67">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU67">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV67">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW67">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX67">
         <v>16</v>
@@ -17744,7 +17744,7 @@
         <v>15.5</v>
       </c>
       <c r="BA67">
-        <v>32</v>
+        <v>5.7</v>
       </c>
       <c r="BB67">
         <v>5.9</v>
@@ -17762,7 +17762,7 @@
         <v>5.7</v>
       </c>
       <c r="BG67">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH67">
         <v>1000</v>
@@ -17845,7 +17845,7 @@
         <v>360</v>
       </c>
       <c r="F68">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="G68">
         <v>1.97</v>
@@ -17854,13 +17854,13 @@
         <v>4.2</v>
       </c>
       <c r="I68">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J68">
         <v>3.9</v>
       </c>
       <c r="K68">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L68">
         <v>1.23</v>
@@ -17872,19 +17872,19 @@
         <v>4.7</v>
       </c>
       <c r="O68">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P68">
         <v>2.26</v>
       </c>
       <c r="Q68">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R68">
         <v>1.5</v>
       </c>
       <c r="S68">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T68">
         <v>1.65</v>
@@ -17893,7 +17893,7 @@
         <v>2.34</v>
       </c>
       <c r="V68">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W68">
         <v>2.02</v>
@@ -17935,7 +17935,7 @@
         <v>55</v>
       </c>
       <c r="AJ68">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK68">
         <v>22</v>
@@ -17986,7 +17986,7 @@
         <v>5.3</v>
       </c>
       <c r="BA68">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB68">
         <v>16</v>
@@ -18004,67 +18004,67 @@
         <v>9</v>
       </c>
       <c r="BG68">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH68">
         <v>1000</v>
       </c>
       <c r="BI68">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BJ68">
         <v>12.5</v>
       </c>
       <c r="BK68">
-        <v>5.9</v>
+        <v>1.71</v>
       </c>
       <c r="BL68">
         <v>1000</v>
       </c>
       <c r="BM68">
-        <v>21</v>
+        <v>1.98</v>
       </c>
       <c r="BN68">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO68">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BP68">
         <v>18</v>
       </c>
       <c r="BQ68">
-        <v>8.199999999999999</v>
+        <v>1.79</v>
       </c>
       <c r="BR68">
         <v>32</v>
       </c>
       <c r="BS68">
-        <v>14.5</v>
+        <v>1.87</v>
       </c>
       <c r="BT68">
         <v>10.5</v>
       </c>
       <c r="BU68">
-        <v>5.1</v>
+        <v>1.67</v>
       </c>
       <c r="BV68">
         <v>44</v>
       </c>
       <c r="BW68">
-        <v>18.5</v>
+        <v>1.9</v>
       </c>
       <c r="BX68">
         <v>1000</v>
       </c>
       <c r="BY68">
-        <v>21</v>
+        <v>1.91</v>
       </c>
       <c r="BZ68">
         <v>25</v>
       </c>
       <c r="CA68">
-        <v>11.5</v>
+        <v>1.84</v>
       </c>
       <c r="CB68" t="s">
         <v>421</v>
@@ -18093,7 +18093,7 @@
         <v>1.41</v>
       </c>
       <c r="H69">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I69">
         <v>10.5</v>
@@ -18126,13 +18126,13 @@
         <v>1.54</v>
       </c>
       <c r="S69">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T69">
         <v>2.02</v>
       </c>
       <c r="U69">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V69">
         <v>1.1</v>
@@ -18144,10 +18144,10 @@
         <v>23</v>
       </c>
       <c r="Y69">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z69">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA69">
         <v>370</v>
@@ -18156,7 +18156,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC69">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD69">
         <v>36</v>
@@ -18174,7 +18174,7 @@
         <v>27</v>
       </c>
       <c r="AI69">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ69">
         <v>12.5</v>
@@ -18201,10 +18201,10 @@
         <v>27</v>
       </c>
       <c r="AR69">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS69">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT69">
         <v>8.800000000000001</v>
@@ -18216,7 +18216,7 @@
         <v>28</v>
       </c>
       <c r="AW69">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX69">
         <v>8</v>
@@ -18228,7 +18228,7 @@
         <v>23</v>
       </c>
       <c r="BA69">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB69">
         <v>10</v>
@@ -18246,67 +18246,67 @@
         <v>5</v>
       </c>
       <c r="BG69">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH69">
         <v>1000</v>
       </c>
       <c r="BI69">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="BJ69">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK69">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="BL69">
         <v>1000</v>
       </c>
       <c r="BM69">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BN69">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO69">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BP69">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ69">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR69">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS69">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="BT69">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BU69">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="BV69">
         <v>1000</v>
       </c>
       <c r="BW69">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BX69">
         <v>1000</v>
       </c>
       <c r="BY69">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ69">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA69">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="CB69" t="s">
         <v>421</v>
@@ -18341,7 +18341,7 @@
         <v>990</v>
       </c>
       <c r="J70">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K70">
         <v>670</v>
@@ -18353,22 +18353,22 @@
         <v>1.01</v>
       </c>
       <c r="N70">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="O70">
         <v>1.35</v>
       </c>
       <c r="P70">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Q70">
-        <v>1.34</v>
+        <v>2.28</v>
       </c>
       <c r="R70">
         <v>1.18</v>
       </c>
       <c r="S70">
-        <v>1.35</v>
+        <v>2.28</v>
       </c>
       <c r="T70">
         <v>1.11</v>
@@ -18571,7 +18571,7 @@
         <v>363</v>
       </c>
       <c r="F71">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G71">
         <v>2.2</v>
@@ -18598,22 +18598,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="O71">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P71">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q71">
         <v>1.3</v>
       </c>
       <c r="R71">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S71">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="T71">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="U71">
         <v>3.35</v>
@@ -18625,7 +18625,7 @@
         <v>1.84</v>
       </c>
       <c r="X71">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="Y71">
         <v>46</v>
@@ -18822,7 +18822,7 @@
         <v>1.9</v>
       </c>
       <c r="I72">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J72">
         <v>4.2</v>
@@ -18858,10 +18858,10 @@
         <v>1.5</v>
       </c>
       <c r="U72">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V72">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="W72">
         <v>1.33</v>
@@ -19005,7 +19005,7 @@
         <v>7.2</v>
       </c>
       <c r="BR72">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS72">
         <v>7.6</v>
@@ -19014,7 +19014,7 @@
         <v>5.6</v>
       </c>
       <c r="BU72">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BV72">
         <v>13</v>
@@ -19032,7 +19032,7 @@
         <v>13.5</v>
       </c>
       <c r="CA72">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="CB72" t="s">
         <v>421</v>
@@ -19055,22 +19055,22 @@
         <v>365</v>
       </c>
       <c r="F73">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G73">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="H73">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="I73">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J73">
         <v>3.35</v>
       </c>
       <c r="K73">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="L73">
         <v>1.01</v>
@@ -19103,10 +19103,10 @@
         <v>1.11</v>
       </c>
       <c r="V73">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W73">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="X73">
         <v>1000</v>
@@ -19297,7 +19297,7 @@
         <v>366</v>
       </c>
       <c r="F74">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="G74">
         <v>4.1</v>
@@ -19327,16 +19327,16 @@
         <v>1.14</v>
       </c>
       <c r="P74">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="Q74">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R74">
         <v>1.74</v>
       </c>
       <c r="S74">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="T74">
         <v>1.47</v>
@@ -19548,10 +19548,10 @@
         <v>2.22</v>
       </c>
       <c r="I75">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J75">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K75">
         <v>500</v>
@@ -19563,22 +19563,22 @@
         <v>1.01</v>
       </c>
       <c r="N75">
-        <v>2.92</v>
+        <v>1.1</v>
       </c>
       <c r="O75">
         <v>1.1</v>
       </c>
       <c r="P75">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q75">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="R75">
         <v>1.86</v>
       </c>
       <c r="S75">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="T75">
         <v>1.11</v>
@@ -19587,7 +19587,7 @@
         <v>1.11</v>
       </c>
       <c r="V75">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W75">
         <v>2.18</v>
@@ -19781,22 +19781,22 @@
         <v>368</v>
       </c>
       <c r="F76">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="G76">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="H76">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="I76">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="J76">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="K76">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="L76">
         <v>1.01</v>
@@ -19805,7 +19805,7 @@
         <v>1.02</v>
       </c>
       <c r="N76">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="O76">
         <v>1.14</v>
@@ -19817,22 +19817,22 @@
         <v>1.41</v>
       </c>
       <c r="R76">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S76">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T76">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U76">
         <v>2.38</v>
       </c>
       <c r="V76">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="W76">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X76">
         <v>36</v>
@@ -19847,22 +19847,22 @@
         <v>14</v>
       </c>
       <c r="AB76">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AC76">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD76">
         <v>11.5</v>
       </c>
       <c r="AE76">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AF76">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AG76">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AH76">
         <v>22</v>
@@ -19877,19 +19877,19 @@
         <v>110</v>
       </c>
       <c r="AL76">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AM76">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AN76">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AO76">
         <v>4.4</v>
       </c>
       <c r="AP76">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ76">
         <v>12</v>
@@ -19901,7 +19901,7 @@
         <v>11.5</v>
       </c>
       <c r="AT76">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AU76">
         <v>11.5</v>
@@ -19913,10 +19913,10 @@
         <v>11.5</v>
       </c>
       <c r="AX76">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AY76">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AZ76">
         <v>17.5</v>
@@ -19925,22 +19925,22 @@
         <v>21</v>
       </c>
       <c r="BB76">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC76">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BD76">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE76">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF76">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG76">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="BH76">
         <v>1000</v>
@@ -20023,19 +20023,19 @@
         <v>369</v>
       </c>
       <c r="F77">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="G77">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H77">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I77">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J77">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K77">
         <v>4.5</v>
@@ -20071,7 +20071,7 @@
         <v>2.4</v>
       </c>
       <c r="V77">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W77">
         <v>2.18</v>
@@ -20101,13 +20101,13 @@
         <v>60</v>
       </c>
       <c r="AF77">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG77">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH77">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI77">
         <v>60</v>
@@ -20137,10 +20137,10 @@
         <v>19</v>
       </c>
       <c r="AR77">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AS77">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT77">
         <v>10.5</v>
@@ -20152,7 +20152,7 @@
         <v>16</v>
       </c>
       <c r="AW77">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX77">
         <v>11.5</v>
@@ -20164,7 +20164,7 @@
         <v>14.5</v>
       </c>
       <c r="BA77">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB77">
         <v>17</v>
@@ -20173,16 +20173,16 @@
         <v>15</v>
       </c>
       <c r="BD77">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE77">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF77">
         <v>6.2</v>
       </c>
       <c r="BG77">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BH77">
         <v>1000</v>
@@ -20280,7 +20280,7 @@
         <v>3.85</v>
       </c>
       <c r="K78">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L78">
         <v>1.01</v>
@@ -20409,7 +20409,7 @@
         <v>27</v>
       </c>
       <c r="BB78">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BC78">
         <v>30</v>
@@ -20537,7 +20537,7 @@
         <v>1.25</v>
       </c>
       <c r="P79">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q79">
         <v>1.77</v>
@@ -20761,7 +20761,7 @@
         <v>5.2</v>
       </c>
       <c r="J80">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K80">
         <v>6</v>
@@ -21009,7 +21009,7 @@
         <v>3.8</v>
       </c>
       <c r="L81">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="M81">
         <v>1.06</v>
@@ -21266,7 +21266,7 @@
         <v>1.24</v>
       </c>
       <c r="Q82">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="R82">
         <v>1.18</v>
@@ -21735,7 +21735,7 @@
         <v>3.8</v>
       </c>
       <c r="L84">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M84">
         <v>1.06</v>
@@ -21759,10 +21759,10 @@
         <v>3.2</v>
       </c>
       <c r="T84">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U84">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V84">
         <v>1.43</v>
@@ -21834,7 +21834,7 @@
         <v>18.5</v>
       </c>
       <c r="AS84">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="AT84">
         <v>9.800000000000001</v>
@@ -21882,10 +21882,10 @@
         <v>1000</v>
       </c>
       <c r="BI84">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BJ84">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK84">
         <v>1.61</v>
@@ -21894,49 +21894,49 @@
         <v>1000</v>
       </c>
       <c r="BM84">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BN84">
         <v>7.6</v>
       </c>
       <c r="BO84">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BP84">
         <v>26</v>
       </c>
       <c r="BQ84">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="BR84">
         <v>44</v>
       </c>
       <c r="BS84">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="BT84">
         <v>9</v>
       </c>
       <c r="BU84">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV84">
         <v>36</v>
       </c>
       <c r="BW84">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="BX84">
         <v>50</v>
       </c>
       <c r="BY84">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="BZ84">
         <v>36</v>
       </c>
       <c r="CA84">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CB84" t="s">
         <v>421</v>
@@ -21959,7 +21959,7 @@
         <v>377</v>
       </c>
       <c r="F85">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="G85">
         <v>2.28</v>
@@ -21971,10 +21971,10 @@
         <v>7.6</v>
       </c>
       <c r="J85">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K85">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="L85">
         <v>1.01</v>
@@ -21992,7 +21992,7 @@
         <v>1.84</v>
       </c>
       <c r="Q85">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R85">
         <v>1.28</v>
@@ -22007,7 +22007,7 @@
         <v>1.11</v>
       </c>
       <c r="V85">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="W85">
         <v>1.78</v>
@@ -22210,7 +22210,7 @@
         <v>5.4</v>
       </c>
       <c r="I86">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="J86">
         <v>3.45</v>
@@ -22225,10 +22225,10 @@
         <v>1.09</v>
       </c>
       <c r="N86">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="O86">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P86">
         <v>1.69</v>
@@ -22237,7 +22237,7 @@
         <v>2.22</v>
       </c>
       <c r="R86">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S86">
         <v>3.9</v>
@@ -22309,7 +22309,7 @@
         <v>180</v>
       </c>
       <c r="AP86">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ86">
         <v>11.5</v>
@@ -22321,10 +22321,10 @@
         <v>4.3</v>
       </c>
       <c r="AT86">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AU86">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV86">
         <v>16.5</v>
@@ -22333,22 +22333,22 @@
         <v>4.2</v>
       </c>
       <c r="AX86">
+        <v>7.4</v>
+      </c>
+      <c r="AY86">
         <v>8.6</v>
       </c>
-      <c r="AY86">
-        <v>9</v>
-      </c>
       <c r="AZ86">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA86">
         <v>4.3</v>
       </c>
       <c r="BB86">
-        <v>3.75</v>
+        <v>14</v>
       </c>
       <c r="BC86">
-        <v>3.8</v>
+        <v>16</v>
       </c>
       <c r="BD86">
         <v>4.1</v>
@@ -22452,7 +22452,7 @@
         <v>1.96</v>
       </c>
       <c r="I87">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="J87">
         <v>3.95</v>
@@ -22709,7 +22709,7 @@
         <v>1.04</v>
       </c>
       <c r="N88">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="O88">
         <v>1.23</v>
@@ -22718,22 +22718,22 @@
         <v>2.06</v>
       </c>
       <c r="Q88">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="R88">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S88">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="T88">
         <v>1.64</v>
       </c>
       <c r="U88">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V88">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W88">
         <v>1.7</v>
@@ -22951,13 +22951,13 @@
         <v>1.01</v>
       </c>
       <c r="N89">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O89">
         <v>1.17</v>
       </c>
       <c r="P89">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q89">
         <v>1.17</v>
@@ -22966,7 +22966,7 @@
         <v>1.18</v>
       </c>
       <c r="S89">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="T89">
         <v>1.11</v>
@@ -23429,7 +23429,7 @@
         <v>7.4</v>
       </c>
       <c r="L91">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M91">
         <v>1.01</v>
@@ -23671,7 +23671,7 @@
         <v>4.5</v>
       </c>
       <c r="L92">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M92">
         <v>1.01</v>
@@ -24146,7 +24146,7 @@
         <v>1.04</v>
       </c>
       <c r="I94">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c r="J94">
         <v>1.08</v>
@@ -24397,7 +24397,7 @@
         <v>5.3</v>
       </c>
       <c r="L95">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M95">
         <v>1.02</v>
@@ -24651,7 +24651,7 @@
         <v>1.33</v>
       </c>
       <c r="P96">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -24660,7 +24660,7 @@
         <v>1.31</v>
       </c>
       <c r="S96">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T96">
         <v>1.11</v>
@@ -24908,7 +24908,7 @@
         <v>1.7</v>
       </c>
       <c r="U97">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="V97">
         <v>2.24</v>
@@ -25028,37 +25028,37 @@
         <v>1000</v>
       </c>
       <c r="BI97">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BJ97">
         <v>14.5</v>
       </c>
       <c r="BK97">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BL97">
         <v>1000</v>
       </c>
       <c r="BM97">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BN97">
         <v>12.5</v>
       </c>
       <c r="BO97">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BP97">
         <v>1000</v>
       </c>
       <c r="BQ97">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BR97">
         <v>1000</v>
       </c>
       <c r="BS97">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BT97">
         <v>5.8</v>
@@ -25070,19 +25070,19 @@
         <v>16</v>
       </c>
       <c r="BW97">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BX97">
         <v>38</v>
       </c>
       <c r="BY97">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BZ97">
         <v>30</v>
       </c>
       <c r="CA97">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="CB97" t="s">
         <v>421</v>
@@ -25383,10 +25383,10 @@
         <v>1.47</v>
       </c>
       <c r="R99">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S99">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="T99">
         <v>1.11</v>
@@ -25592,16 +25592,16 @@
         <v>5.1</v>
       </c>
       <c r="G100">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H100">
         <v>1.83</v>
       </c>
       <c r="I100">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="J100">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K100">
         <v>3.9</v>
@@ -25616,34 +25616,34 @@
         <v>2.58</v>
       </c>
       <c r="O100">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P100">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q100">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R100">
         <v>1.18</v>
       </c>
       <c r="S100">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="T100">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U100">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="V100">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W100">
         <v>1.19</v>
       </c>
       <c r="X100">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y100">
         <v>7.4</v>
@@ -25688,16 +25688,16 @@
         <v>160</v>
       </c>
       <c r="AM100">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AN100">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AO100">
         <v>28</v>
       </c>
       <c r="AP100">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ100">
         <v>4.7</v>
@@ -25721,34 +25721,34 @@
         <v>19.5</v>
       </c>
       <c r="AX100">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AY100">
         <v>17</v>
       </c>
       <c r="AZ100">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA100">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BB100">
         <v>4.3</v>
       </c>
       <c r="BC100">
+        <v>4.2</v>
+      </c>
+      <c r="BD100">
+        <v>4.2</v>
+      </c>
+      <c r="BE100">
         <v>4.3</v>
-      </c>
-      <c r="BD100">
-        <v>4.3</v>
-      </c>
-      <c r="BE100">
-        <v>4.4</v>
       </c>
       <c r="BF100">
         <v>4.3</v>
       </c>
       <c r="BG100">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH100">
         <v>1000</v>
@@ -25834,7 +25834,7 @@
         <v>2.3</v>
       </c>
       <c r="G101">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H101">
         <v>3.35</v>
@@ -25852,7 +25852,7 @@
         <v>1.01</v>
       </c>
       <c r="M101">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N101">
         <v>3.55</v>
@@ -25861,7 +25861,7 @@
         <v>1.33</v>
       </c>
       <c r="P101">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q101">
         <v>1.98</v>
@@ -25924,16 +25924,16 @@
         <v>32</v>
       </c>
       <c r="AK101">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL101">
         <v>42</v>
       </c>
       <c r="AM101">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN101">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO101">
         <v>42</v>
@@ -25984,7 +25984,7 @@
         <v>34</v>
       </c>
       <c r="BE101">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF101">
         <v>17.5</v>
@@ -26097,16 +26097,16 @@
         <v>1.01</v>
       </c>
       <c r="N102">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O102">
         <v>1.01</v>
       </c>
       <c r="P102">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q102">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R102">
         <v>1.12</v>
@@ -26315,22 +26315,22 @@
         <v>395</v>
       </c>
       <c r="F103">
-        <v>6.4</v>
+        <v>1.89</v>
       </c>
       <c r="G103">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="H103">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="I103">
-        <v>1.59</v>
+        <v>2.48</v>
       </c>
       <c r="J103">
-        <v>3.75</v>
+        <v>1.7</v>
       </c>
       <c r="K103">
-        <v>6.6</v>
+        <v>110</v>
       </c>
       <c r="L103">
         <v>1.01</v>
@@ -26339,7 +26339,7 @@
         <v>1.01</v>
       </c>
       <c r="N103">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O103">
         <v>1.35</v>
@@ -26363,10 +26363,10 @@
         <v>1.11</v>
       </c>
       <c r="V103">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="W103">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X103">
         <v>1000</v>
@@ -26486,55 +26486,55 @@
         <v>1000</v>
       </c>
       <c r="BK103">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BL103">
         <v>1000</v>
       </c>
       <c r="BM103">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BN103">
         <v>1000</v>
       </c>
       <c r="BO103">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BP103">
         <v>1000</v>
       </c>
       <c r="BQ103">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BR103">
         <v>1000</v>
       </c>
       <c r="BS103">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BT103">
         <v>1000</v>
       </c>
       <c r="BU103">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BV103">
         <v>1000</v>
       </c>
       <c r="BW103">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BX103">
         <v>1000</v>
       </c>
       <c r="BY103">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BZ103">
         <v>1000</v>
       </c>
       <c r="CA103">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="CB103" t="s">
         <v>421</v>
@@ -26722,19 +26722,19 @@
         <v>1000</v>
       </c>
       <c r="BI104">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="BJ104">
         <v>15.5</v>
       </c>
       <c r="BK104">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="BL104">
         <v>1000</v>
       </c>
       <c r="BM104">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="BN104">
         <v>7.8</v>
@@ -26746,13 +26746,13 @@
         <v>36</v>
       </c>
       <c r="BQ104">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BR104">
         <v>1000</v>
       </c>
       <c r="BS104">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BT104">
         <v>8.199999999999999</v>
@@ -26764,19 +26764,19 @@
         <v>38</v>
       </c>
       <c r="BW104">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BX104">
         <v>1000</v>
       </c>
       <c r="BY104">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BZ104">
         <v>1000</v>
       </c>
       <c r="CA104">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="CB104" t="s">
         <v>421</v>
@@ -26811,7 +26811,7 @@
         <v>990</v>
       </c>
       <c r="J105">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="K105">
         <v>950</v>
@@ -26823,16 +26823,16 @@
         <v>1.01</v>
       </c>
       <c r="N105">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="O105">
         <v>1.01</v>
       </c>
       <c r="P105">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q105">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R105">
         <v>1.12</v>
@@ -27065,10 +27065,10 @@
         <v>1.01</v>
       </c>
       <c r="N106">
-        <v>2.66</v>
+        <v>5.7</v>
       </c>
       <c r="O106">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P106">
         <v>2.68</v>
@@ -27077,16 +27077,16 @@
         <v>1.49</v>
       </c>
       <c r="R106">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="S106">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="T106">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="U106">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="V106">
         <v>1.23</v>
@@ -27095,112 +27095,112 @@
         <v>2.26</v>
       </c>
       <c r="X106">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y106">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z106">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA106">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB106">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC106">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD106">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE106">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF106">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG106">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH106">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI106">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ106">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK106">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL106">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM106">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN106">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO106">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP106">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ106">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AR106">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AS106">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="AT106">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU106">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV106">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW106">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AX106">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY106">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ106">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA106">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BB106">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC106">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD106">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE106">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BF106">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG106">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BH106">
         <v>1000</v>
@@ -27289,7 +27289,7 @@
         <v>1.88</v>
       </c>
       <c r="H107">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I107">
         <v>990</v>
@@ -27298,7 +27298,7 @@
         <v>2.22</v>
       </c>
       <c r="K107">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L107">
         <v>1.36</v>
@@ -27331,7 +27331,7 @@
         <v>1.11</v>
       </c>
       <c r="V107">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="W107">
         <v>2.14</v>
@@ -27525,7 +27525,7 @@
         <v>400</v>
       </c>
       <c r="F108">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G108">
         <v>2.38</v>
@@ -27546,19 +27546,19 @@
         <v>1.01</v>
       </c>
       <c r="M108">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N108">
-        <v>2.04</v>
+        <v>1.1</v>
       </c>
       <c r="O108">
         <v>1.44</v>
       </c>
       <c r="P108">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q108">
-        <v>2.16</v>
+        <v>1.89</v>
       </c>
       <c r="R108">
         <v>1.18</v>
@@ -27573,7 +27573,7 @@
         <v>1.11</v>
       </c>
       <c r="V108">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W108">
         <v>1.72</v>
@@ -27770,19 +27770,19 @@
         <v>2.14</v>
       </c>
       <c r="G109">
-        <v>2.96</v>
+        <v>2.64</v>
       </c>
       <c r="H109">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I109">
         <v>4.8</v>
       </c>
       <c r="J109">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="K109">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="L109">
         <v>1.5</v>
@@ -27794,7 +27794,7 @@
         <v>2.2</v>
       </c>
       <c r="O109">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="P109">
         <v>1.37</v>
@@ -27818,7 +27818,7 @@
         <v>1.26</v>
       </c>
       <c r="W109">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="X109">
         <v>11</v>
@@ -28012,7 +28012,7 @@
         <v>2.28</v>
       </c>
       <c r="G110">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="H110">
         <v>3.1</v>
@@ -28045,13 +28045,13 @@
         <v>1.86</v>
       </c>
       <c r="R110">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S110">
         <v>3.05</v>
       </c>
       <c r="T110">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U110">
         <v>1.11</v>
@@ -28060,7 +28060,7 @@
         <v>1.38</v>
       </c>
       <c r="W110">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X110">
         <v>1000</v>
@@ -28511,7 +28511,7 @@
         <v>5.9</v>
       </c>
       <c r="L112">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M112">
         <v>1.01</v>
@@ -28995,19 +28995,19 @@
         <v>0</v>
       </c>
       <c r="L114">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M114">
         <v>1.01</v>
       </c>
       <c r="N114">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O114">
         <v>1.27</v>
       </c>
       <c r="P114">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q114">
         <v>1.27</v>
@@ -29219,10 +29219,10 @@
         <v>407</v>
       </c>
       <c r="F115">
-        <v>1.8</v>
+        <v>2.52</v>
       </c>
       <c r="G115">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="H115">
         <v>2.5</v>
@@ -29243,13 +29243,13 @@
         <v>1.04</v>
       </c>
       <c r="N115">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="O115">
         <v>1.41</v>
       </c>
       <c r="P115">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Q115">
         <v>1.4</v>
@@ -29282,7 +29282,7 @@
         <v>27</v>
       </c>
       <c r="AA115">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB115">
         <v>30</v>
@@ -29294,7 +29294,7 @@
         <v>18</v>
       </c>
       <c r="AE115">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF115">
         <v>34</v>
@@ -29303,10 +29303,10 @@
         <v>22</v>
       </c>
       <c r="AH115">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI115">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ115">
         <v>100</v>
@@ -29315,22 +29315,22 @@
         <v>90</v>
       </c>
       <c r="AL115">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AM115">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="AN115">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AO115">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP115">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AQ115">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AR115">
         <v>12</v>
@@ -29339,7 +29339,7 @@
         <v>28</v>
       </c>
       <c r="AT115">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AU115">
         <v>5.9</v>
@@ -29348,7 +29348,7 @@
         <v>9.4</v>
       </c>
       <c r="AW115">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AX115">
         <v>15.5</v>
@@ -29357,22 +29357,22 @@
         <v>11</v>
       </c>
       <c r="AZ115">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BA115">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BB115">
         <v>38</v>
       </c>
       <c r="BC115">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="BD115">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="BE115">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="BF115">
         <v>9</v>
@@ -29479,7 +29479,7 @@
         <v>3.6</v>
       </c>
       <c r="L116">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="M116">
         <v>1.08</v>
@@ -29500,7 +29500,7 @@
         <v>1.3</v>
       </c>
       <c r="S116">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="T116">
         <v>1.83</v>
@@ -29569,7 +29569,7 @@
         <v>60</v>
       </c>
       <c r="AP116">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ116">
         <v>10.5</v>
@@ -29584,7 +29584,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU116">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AV116">
         <v>11</v>
@@ -29703,7 +29703,7 @@
         <v>409</v>
       </c>
       <c r="F117">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="G117">
         <v>3</v>
@@ -29715,7 +29715,7 @@
         <v>5.5</v>
       </c>
       <c r="J117">
-        <v>2.06</v>
+        <v>2.78</v>
       </c>
       <c r="K117">
         <v>500</v>
@@ -29730,7 +29730,7 @@
         <v>1.4</v>
       </c>
       <c r="O117">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="P117">
         <v>1.4</v>
@@ -29948,7 +29948,7 @@
         <v>1.65</v>
       </c>
       <c r="G118">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="H118">
         <v>4.8</v>
@@ -29963,7 +29963,7 @@
         <v>4</v>
       </c>
       <c r="L118">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M118">
         <v>1.01</v>
@@ -29972,13 +29972,13 @@
         <v>2.74</v>
       </c>
       <c r="O118">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P118">
         <v>1.25</v>
       </c>
       <c r="Q118">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R118">
         <v>1.22</v>
@@ -29996,7 +29996,7 @@
         <v>1.16</v>
       </c>
       <c r="W118">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="X118">
         <v>16.5</v>
@@ -30190,7 +30190,7 @@
         <v>2.44</v>
       </c>
       <c r="G119">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H119">
         <v>3.3</v>
@@ -30205,22 +30205,22 @@
         <v>3.25</v>
       </c>
       <c r="L119">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="M119">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N119">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="O119">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="P119">
         <v>1.17</v>
       </c>
       <c r="Q119">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="R119">
         <v>1.17</v>
@@ -30238,7 +30238,7 @@
         <v>1.32</v>
       </c>
       <c r="W119">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X119">
         <v>1000</v>
@@ -30447,16 +30447,16 @@
         <v>3.6</v>
       </c>
       <c r="L120">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M120">
         <v>1.07</v>
       </c>
       <c r="N120">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="O120">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P120">
         <v>1.89</v>
@@ -30465,130 +30465,130 @@
         <v>2.02</v>
       </c>
       <c r="R120">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S120">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="T120">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U120">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V120">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W120">
         <v>1.73</v>
       </c>
       <c r="X120">
+        <v>14</v>
+      </c>
+      <c r="Y120">
+        <v>13.5</v>
+      </c>
+      <c r="Z120">
+        <v>26</v>
+      </c>
+      <c r="AA120">
+        <v>70</v>
+      </c>
+      <c r="AB120">
+        <v>10</v>
+      </c>
+      <c r="AC120">
+        <v>7.8</v>
+      </c>
+      <c r="AD120">
         <v>16</v>
       </c>
-      <c r="Y120">
+      <c r="AE120">
+        <v>46</v>
+      </c>
+      <c r="AF120">
         <v>15.5</v>
       </c>
-      <c r="Z120">
-        <v>30</v>
-      </c>
-      <c r="AA120">
-        <v>80</v>
-      </c>
-      <c r="AB120">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC120">
+      <c r="AG120">
+        <v>12</v>
+      </c>
+      <c r="AH120">
+        <v>18.5</v>
+      </c>
+      <c r="AI120">
+        <v>55</v>
+      </c>
+      <c r="AJ120">
+        <v>32</v>
+      </c>
+      <c r="AK120">
+        <v>27</v>
+      </c>
+      <c r="AL120">
+        <v>42</v>
+      </c>
+      <c r="AM120">
+        <v>120</v>
+      </c>
+      <c r="AN120">
+        <v>22</v>
+      </c>
+      <c r="AO120">
+        <v>60</v>
+      </c>
+      <c r="AP120">
+        <v>11</v>
+      </c>
+      <c r="AQ120">
+        <v>11</v>
+      </c>
+      <c r="AR120">
+        <v>21</v>
+      </c>
+      <c r="AS120">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT120">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU120">
+        <v>6.6</v>
+      </c>
+      <c r="AV120">
+        <v>12.5</v>
+      </c>
+      <c r="AW120">
+        <v>7.8</v>
+      </c>
+      <c r="AX120">
+        <v>12</v>
+      </c>
+      <c r="AY120">
+        <v>9.6</v>
+      </c>
+      <c r="AZ120">
+        <v>15.5</v>
+      </c>
+      <c r="BA120">
         <v>8</v>
       </c>
-      <c r="AD120">
-        <v>18.5</v>
-      </c>
-      <c r="AE120">
-        <v>50</v>
-      </c>
-      <c r="AF120">
-        <v>18</v>
-      </c>
-      <c r="AG120">
-        <v>13.5</v>
-      </c>
-      <c r="AH120">
-        <v>22</v>
-      </c>
-      <c r="AI120">
-        <v>65</v>
-      </c>
-      <c r="AJ120">
-        <v>36</v>
-      </c>
-      <c r="AK120">
-        <v>30</v>
-      </c>
-      <c r="AL120">
-        <v>50</v>
-      </c>
-      <c r="AM120">
-        <v>1000</v>
-      </c>
-      <c r="AN120">
-        <v>1000</v>
-      </c>
-      <c r="AO120">
-        <v>1000</v>
-      </c>
-      <c r="AP120">
-        <v>3.15</v>
-      </c>
-      <c r="AQ120">
-        <v>9.4</v>
-      </c>
-      <c r="AR120">
-        <v>3.45</v>
-      </c>
-      <c r="AS120">
-        <v>3.7</v>
-      </c>
-      <c r="AT120">
-        <v>2.8</v>
-      </c>
-      <c r="AU120">
-        <v>2.62</v>
-      </c>
-      <c r="AV120">
-        <v>3.2</v>
-      </c>
-      <c r="AW120">
-        <v>3.6</v>
-      </c>
-      <c r="AX120">
-        <v>10</v>
-      </c>
-      <c r="AY120">
-        <v>3</v>
-      </c>
-      <c r="AZ120">
-        <v>3.3</v>
-      </c>
-      <c r="BA120">
-        <v>3.7</v>
-      </c>
       <c r="BB120">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="BC120">
-        <v>3.45</v>
+        <v>21</v>
       </c>
       <c r="BD120">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE120">
-        <v>3.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF120">
-        <v>2.8</v>
+        <v>17.5</v>
       </c>
       <c r="BG120">
-        <v>2.8</v>
+        <v>32</v>
       </c>
       <c r="BH120">
         <v>1000</v>
@@ -30689,13 +30689,13 @@
         <v>4.1</v>
       </c>
       <c r="L121">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M121">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N121">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="O121">
         <v>1.29</v>
@@ -30704,16 +30704,16 @@
         <v>2</v>
       </c>
       <c r="Q121">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="R121">
         <v>1.38</v>
       </c>
       <c r="S121">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="T121">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U121">
         <v>2.02</v>
@@ -30725,7 +30725,7 @@
         <v>2.2</v>
       </c>
       <c r="X121">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y121">
         <v>21</v>
@@ -30788,49 +30788,49 @@
         <v>26</v>
       </c>
       <c r="AS121">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="AT121">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="AU121">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="AV121">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="AW121">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="AX121">
-        <v>2.36</v>
+        <v>2.74</v>
       </c>
       <c r="AY121">
-        <v>2.32</v>
+        <v>2.68</v>
       </c>
       <c r="AZ121">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="BA121">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="BB121">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="BC121">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="BD121">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="BE121">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="BF121">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="BG121">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="BH121">
         <v>1000</v>
@@ -30919,13 +30919,13 @@
         <v>2.12</v>
       </c>
       <c r="H122">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I122">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="J122">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K122">
         <v>3.7</v>
@@ -30934,13 +30934,13 @@
         <v>1.01</v>
       </c>
       <c r="M122">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N122">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="O122">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P122">
         <v>1.69</v>
@@ -30949,130 +30949,130 @@
         <v>2.22</v>
       </c>
       <c r="R122">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="S122">
-        <v>2.22</v>
+        <v>3.85</v>
       </c>
       <c r="T122">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="U122">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V122">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W122">
         <v>1.89</v>
       </c>
       <c r="X122">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y122">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z122">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA122">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB122">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC122">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD122">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE122">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF122">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG122">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH122">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI122">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ122">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK122">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL122">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM122">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN122">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO122">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP122">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ122">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR122">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AS122">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="AT122">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU122">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV122">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW122">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="AX122">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY122">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ122">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA122">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BB122">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC122">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD122">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE122">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="BF122">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG122">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BH122">
         <v>3.6</v>
@@ -31194,7 +31194,7 @@
         <v>1.24</v>
       </c>
       <c r="S123">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T123">
         <v>1.01</v>
@@ -31421,7 +31421,7 @@
         <v>1.01</v>
       </c>
       <c r="N124">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O124">
         <v>1.06</v>
@@ -31433,7 +31433,7 @@
         <v>1.06</v>
       </c>
       <c r="R124">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S124">
         <v>1.06</v>
@@ -31666,7 +31666,7 @@
         <v>1.18</v>
       </c>
       <c r="O125">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P125">
         <v>1.24</v>
@@ -31678,7 +31678,7 @@
         <v>1.18</v>
       </c>
       <c r="S125">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="T125">
         <v>1.01</v>
@@ -31890,7 +31890,7 @@
         <v>3.95</v>
       </c>
       <c r="I126">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J126">
         <v>3</v>
@@ -31899,13 +31899,13 @@
         <v>3.25</v>
       </c>
       <c r="L126">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="M126">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N126">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O126">
         <v>1.57</v>
@@ -31914,133 +31914,133 @@
         <v>1.51</v>
       </c>
       <c r="Q126">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="R126">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S126">
-        <v>2.68</v>
+        <v>5.7</v>
       </c>
       <c r="T126">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U126">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="V126">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W126">
         <v>1.73</v>
       </c>
       <c r="X126">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Y126">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z126">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA126">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB126">
         <v>7</v>
       </c>
       <c r="AC126">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD126">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE126">
         <v>80</v>
       </c>
       <c r="AF126">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG126">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH126">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI126">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ126">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK126">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL126">
         <v>65</v>
       </c>
       <c r="AM126">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN126">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO126">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP126">
-        <v>1.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ126">
-        <v>1.39</v>
+        <v>9.4</v>
       </c>
       <c r="AR126">
-        <v>1.39</v>
+        <v>5.3</v>
       </c>
       <c r="AS126">
-        <v>1.39</v>
+        <v>6</v>
       </c>
       <c r="AT126">
-        <v>1.16</v>
+        <v>6</v>
       </c>
       <c r="AU126">
-        <v>1.39</v>
+        <v>6.4</v>
       </c>
       <c r="AV126">
-        <v>1.39</v>
+        <v>16</v>
       </c>
       <c r="AW126">
-        <v>1.36</v>
+        <v>5.9</v>
       </c>
       <c r="AX126">
-        <v>1.39</v>
+        <v>11</v>
       </c>
       <c r="AY126">
-        <v>1.39</v>
+        <v>10.5</v>
       </c>
       <c r="AZ126">
-        <v>1.39</v>
+        <v>5.2</v>
       </c>
       <c r="BA126">
-        <v>1.39</v>
+        <v>6</v>
       </c>
       <c r="BB126">
-        <v>1.39</v>
+        <v>5.4</v>
       </c>
       <c r="BC126">
-        <v>1.39</v>
+        <v>5.4</v>
       </c>
       <c r="BD126">
-        <v>1.36</v>
+        <v>5.8</v>
       </c>
       <c r="BE126">
-        <v>1.39</v>
+        <v>6.2</v>
       </c>
       <c r="BF126">
-        <v>1.39</v>
+        <v>5.5</v>
       </c>
       <c r="BG126">
-        <v>1.39</v>
+        <v>6</v>
       </c>
       <c r="BH126">
         <v>3.1</v>
@@ -32123,22 +32123,22 @@
         <v>419</v>
       </c>
       <c r="F127">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="G127">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="H127">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="I127">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="J127">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K127">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L127">
         <v>1.01</v>
@@ -32147,22 +32147,22 @@
         <v>1.01</v>
       </c>
       <c r="N127">
-        <v>1.24</v>
+        <v>2.6</v>
       </c>
       <c r="O127">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="P127">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q127">
-        <v>1.44</v>
+        <v>2.42</v>
       </c>
       <c r="R127">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S127">
-        <v>1.02</v>
+        <v>2.42</v>
       </c>
       <c r="T127">
         <v>1.01</v>
@@ -32231,52 +32231,52 @@
         <v>1000</v>
       </c>
       <c r="AP127">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ127">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AR127">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS127">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AT127">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU127">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV127">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW127">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX127">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AY127">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AZ127">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA127">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB127">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BC127">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BD127">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BE127">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BF127">
         <v>1.01</v>
@@ -32365,7 +32365,7 @@
         <v>420</v>
       </c>
       <c r="F128">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="G128">
         <v>11</v>
@@ -32374,25 +32374,25 @@
         <v>1.56</v>
       </c>
       <c r="I128">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="J128">
         <v>3.75</v>
       </c>
       <c r="K128">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="L128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P128">
         <v>1.75</v>
@@ -32401,190 +32401,190 @@
         <v>1.98</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V128">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="W128">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP128">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ128">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AR128">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AS128">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AT128">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AU128">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV128">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AW128">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AX128">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AY128">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AZ128">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA128">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BB128">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BC128">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BD128">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE128">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI128">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BJ128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ128">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB128" t="s">
         <v>421</v>
